--- a/mapping/PDTD_DTM/Mapping_FCT_RLOS_APPLICATION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_RLOS_APPLICATION.xlsx
@@ -411,8 +411,8 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Fact hồ sơ tín dụng RLOS tại PDTD_DTM, relay 1:1 các cột gốc từ STG_DTM.STG_FCT_RLOS_APPLICATION, bổ sung user xử lý từng bước, cờ carry-forward tiến trình, business rule trạng thái/auto-cancel, và tra cứu SLA/luồng nghiệp vụ</t>
+          <t>Bảng FACT hồ sơ tín dụng RLOS tại PDTD_DTM — bê nguyên 1:1 phần lớn cột từ STG_DTM.STG_FCT_RLOS_APPLICATION, bổ sung khóa T24, user theo bước, SLA, cờ carry-forward</t>
         </is>
       </c>
       <c r="E2" s="52" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="A5" s="13" t="n"/>
       <c r="E5" s="52" t="inlineStr">
         <is>
-          <t>STG_FCT_RLOS_WORKSTEP_EVENT AS E2</t>
+          <t>STG_FCT_RLOS_WORKSTEP_EVENT AS E (alias WE nội bộ)</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       <c r="A6" s="13" t="n"/>
       <c r="E6" s="52" t="inlineStr">
         <is>
-          <t>STG_DIM_RLOS_WORKSTEP_DECISION AS F</t>
+          <t>STG_DIM_RLOS_WORKSTEP_DECISION AS F (alias WD nội bộ)</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="inlineStr">
         <is>
-          <t>RLOS_REF_SLA_TDKHCN AS J</t>
+          <t>DIM_RLOS_PRODUCT AS J</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="inlineStr">
         <is>
-          <t>DIM_RLOS_PRODUCT AS K</t>
+          <t>RLOS_REF_SLA_TDKHCN AS K</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="inlineStr">
         <is>
-          <t>FCT_RLOS_APPLICATION_PREV AS L</t>
+          <t>FCT_RLOS_APPLICATION_PREV AS L (alias p)</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Ngày dữ liệu, dạng số YYYYMMDD — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.DAYID</t>
+          <t>Ngày dữ liệu, dạng số YYYYMMDD — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.DAYID</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
@@ -962,37 +962,37 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="60" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
-          <t>WORKSTEP_DECISION_SK</t>
+          <t>WI_NAME</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới bước xử lý - quyết định gần nhất</t>
+          <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. Mặc định -1 — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.WORKSTEP_DECISION_SK (đổi tên từ LAST_WORKSTEP_DECISION_SK đồng bộ pattern CLOS)</t>
+          <t>PK (2/2) — Mã hồ sơ tín dụng RLOS — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.WI_NAME</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>A.WORKSTEP_DECISION_SK</t>
+          <t>A.WI_NAME</t>
         </is>
       </c>
     </row>
     <row r="20" ht="60" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
-          <t>SUB_PRODUCT_SK</t>
+          <t>WORKSTEP_DECISION_SK</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
@@ -1002,78 +1002,78 @@
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới sản phẩm vay chi tiết</t>
+          <t>Khóa bước &amp; quyết định cuối</t>
         </is>
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product) — lookup theo PRODUCTLINE_CODE/SUB_PRODUCT_NAME, điều kiện SCD2 hiệu lực tại DAYID. Mặc định -1 nếu không khớp — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.SUB_PRODUCT_SK</t>
+          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. Mặc định -1 — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.WORKSTEP_DECISION_SK (đổi tên từ LAST_WORKSTEP_DECISION_SK)</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>A.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>A.WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_SK</t>
+          <t>WORKSTEP_CODE</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới công ty/tổ chức</t>
+          <t>Mã bước xử lý cuối</t>
         </is>
       </c>
       <c r="D21" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_COMPANY — lookup theo COMPANY_CODE, điều kiện SCD2 hiệu lực tại DAYID. Mặc định -1 nếu không khớp — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.COMPANY_SK</t>
+          <t>CỘT MỚI — BK cạnh SK, 1 phần BK composite (WORKSTEP_CODE+DECISION_CODE) của DIM_RLOS_WORKSTEP_DECISION, giá trị đã có sẵn trong bước lookup WORKSTEP_DECISION_SK</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>A.COMPANY_SK</t>
+          <t>A.WORKSTEP_CODE</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>CHANGE_TYPE_SK</t>
+          <t>DECISION_CODE</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(200)</t>
         </is>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới loại thay đổi điều kiện phê duyệt</t>
+          <t>Mã quyết định cuối</t>
         </is>
       </c>
       <c r="D22" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CHANGE_TYPE. Chỉ có giá trị với hồ sơ thay đổi điều kiện phê duyệt, còn lại Unknown -1 — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_TYPE_SK</t>
+          <t>CỘT MỚI — nửa còn lại BK composite DIM_RLOS_WORKSTEP_DECISION, giá trị đã có sẵn trong bước lookup WORKSTEP_DECISION_SK</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_TYPE_SK</t>
+          <t>A.DECISION_CODE</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>CARD_PROMOTION_SK</t>
+          <t>SUB_PRODUCT_SK</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1083,1352 +1083,1683 @@
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới khuyến mãi thẻ</t>
+          <t>Khóa sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Hồ sơ không phải thẻ dùng -1 — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CARD_PROMOTION_SK</t>
+          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product) — lookup theo PRODUCTLINE_CODE/SUB_PRODUCT_NAME, điều kiện SCD2 hiệu lực tại DAYID</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
         <is>
-          <t>A.CARD_PROMOTION_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>A.SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>T24_CARD_SK</t>
+          <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Mã sản phẩm nhánh</t>
+        </is>
+      </c>
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK thật cạnh SK (layer Sub Product), giá trị đã có sẵn trong bước lookup SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>A.SUB_PRODUCT_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới thẻ T24</t>
-        </is>
-      </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_T24_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH. Báo cáo khai thác K_TYPE qua FK này, không denormalize trực tiếp lên FCT</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C ON C.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN B ON B.MAIN_ID = C.RESULT_MAIN_CARD_ID → B.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>T24_SEAB_MAIN_CARD_SK</t>
-        </is>
-      </c>
-      <c r="B25" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới thẻ chính T24</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_T24_SEAB_MAIN_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH. Báo cáo khai thác HOME_ADDRESS qua FK này, không denormalize trực tiếp lên FCT</t>
+          <t>Khóa tới DIM_LOS_COMPANY — lookup theo COMPANY_CODE, điều kiện SCD2 hiệu lực tại DAYID. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>LEFT JOIN C ON C.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN D ON D.RECID = C.RESULT_MAIN_CARD_ID → D.DIMENSION_KEY</t>
+          <t>A.COMPANY_SK</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>WI_NAME</t>
+          <t>COMPANY_CODE</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Mã đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK (layer Company), cùng giá trị đã dùng để lookup COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>A.COMPANY_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
+        <is>
+          <t>CHANGE_TYPE_SK</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Khóa loại thay đổi</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_CHANGE_TYPE. Chỉ có giá trị với hồ sơ thay đổi điều kiện phê duyệt, còn lại Unknown -1</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_TYPE_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
+          <t>CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C26" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D26" s="54" t="inlineStr">
-        <is>
-          <t>PK (2/2) — Mã hồ sơ tín dụng RLOS — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.WI_NAME</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="45" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Mã loại thay đổi</t>
+        </is>
+      </c>
+      <c r="D28" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, 1 phần BK composite (CHANGE_TYPE_CODE+DETAIL_CHANGE_TYPE_CODE) của DIM_RLOS_CHANGE_TYPE, giá trị đã có sẵn trong bước lookup CHANGE_TYPE_SK</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>DETAIL_CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Mã chi tiết loại thay đổi</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — nửa còn lại BK composite DIM_RLOS_CHANGE_TYPE, giá trị đã có sẵn trong bước lookup CHANGE_TYPE_SK</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>CARD_PROMOTION_SK</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Khóa ưu đãi phí thẻ</t>
+        </is>
+      </c>
+      <c r="D30" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Hồ sơ không phải thẻ dùng -1</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>A.CARD_PROMOTION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>PROMOTION_CODE</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Mã ưu đãi phí</t>
+        </is>
+      </c>
+      <c r="D31" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK, cùng giá trị đã dùng để lookup CARD_PROMOTION_SK</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>A.PROMOTION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>T24_CARD_SK</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Khóa thẻ T24</t>
+        </is>
+      </c>
+      <c r="D32" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_T24_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>B.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>T24_SEAB_MAIN_CARD_SK</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Khóa thẻ chính SEAB</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_T24_SEAB_MAIN_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>D.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
         <is>
           <t>USER_SK</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới người xử lý gần nhất</t>
-        </is>
-      </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Khóa người xử lý</t>
+        </is>
+      </c>
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_LOS_USER của người xử lý sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USER_SK FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.EXITDATE IS NOT NULL AND E2.ENTRYDATE &lt;= v_batch_date ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USER_SK FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
         <is>
           <t>BRANCH_USER</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước BranchSupport</t>
-        </is>
-      </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>User Chi nhánh</t>
+        </is>
+      </c>
+      <c r="D35" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước BranchSupport, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'BranchSupport' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'BranchSupport' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
         <is>
           <t>DDE_USER</t>
         </is>
       </c>
-      <c r="B29" s="25" t="inlineStr">
+      <c r="B36" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước DetailDataEntry</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên viên nhập liệu</t>
+        </is>
+      </c>
+      <c r="D36" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước DetailDataEntry, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'DetailDataEntry' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DetailDataEntry' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>QC_USER</t>
         </is>
       </c>
-      <c r="B30" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước DataInputerChecker</t>
-        </is>
-      </c>
-      <c r="D30" s="54" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>User Kiểm soát nhập liệu</t>
+        </is>
+      </c>
+      <c r="D37" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước DataInputerChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E30" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'DataInputerChecker' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DataInputerChecker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="28" t="inlineStr">
         <is>
           <t>UND_MAKER_USER</t>
         </is>
       </c>
-      <c r="B31" s="25" t="inlineStr">
+      <c r="B38" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước UnderwriterMaker</t>
-        </is>
-      </c>
-      <c r="D31" s="54" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên viên thẩm định</t>
+        </is>
+      </c>
+      <c r="D38" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước UnderwriterMaker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E31" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterMaker' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterMaker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
         <is>
           <t>UND_CHECKER_USER</t>
         </is>
       </c>
-      <c r="B32" s="25" t="inlineStr">
+      <c r="B39" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước UnderwriterChecker</t>
-        </is>
-      </c>
-      <c r="D32" s="54" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>User Kiểm soát thẩm định</t>
+        </is>
+      </c>
+      <c r="D39" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước UnderwriterChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterChecker' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>PHV_USER</t>
-        </is>
-      </c>
-      <c r="B33" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước PhoneVerification</t>
-        </is>
-      </c>
-      <c r="D33" s="54" t="inlineStr">
-        <is>
-          <t>User xử lý bước PhoneVerification, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'PhoneVerification' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>APPROVER_USER</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>User xử lý bước CreditApproval</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>User xử lý bước CreditApproval, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.USERNAME FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'CreditApproval' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>PROCESSED_DATE</t>
-        </is>
-      </c>
-      <c r="B35" s="25" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C35" s="26" t="inlineStr">
-        <is>
-          <t>Ngày xử lý</t>
-        </is>
-      </c>
-      <c r="D35" s="54" t="inlineStr">
-        <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.PROCESSED_DATE</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>A.PROCESSED_DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>CREATION_DATE</t>
-        </is>
-      </c>
-      <c r="B36" s="25" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C36" s="26" t="inlineStr">
-        <is>
-          <t>Ngày tạo hồ sơ</t>
-        </is>
-      </c>
-      <c r="D36" s="54" t="inlineStr">
-        <is>
-          <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CREATION_DATE</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
-        <is>
-          <t>A.CREATION_DATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>LAST_APPROVAL_DATE</t>
-        </is>
-      </c>
-      <c r="B37" s="25" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C37" s="26" t="inlineStr">
-        <is>
-          <t>Ngày phê duyệt gần nhất</t>
-        </is>
-      </c>
-      <c r="D37" s="54" t="inlineStr">
-        <is>
-          <t>MAX(EXITDATE) tại bước phê duyệt (không lọc DECISION) — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT MAX(E2.EXITDATE) FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee'))</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="28" t="inlineStr">
-        <is>
-          <t>MIN_UWM</t>
-        </is>
-      </c>
-      <c r="B38" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C38" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu UnderwriterMaker sớm nhất</t>
-        </is>
-      </c>
-      <c r="D38" s="54" t="inlineStr">
-        <is>
-          <t>MIN(ENTRYDATE) tại UnderwriterMaker — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E38" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT MIN(E2.ENTRYDATE) FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterMaker')</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>MIN_APP</t>
-        </is>
-      </c>
-      <c r="B39" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C39" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm bắt đầu phê duyệt sớm nhất</t>
-        </is>
-      </c>
-      <c r="D39" s="54" t="inlineStr">
-        <is>
-          <t>MIN(ENTRYDATE) tại CreditApproval/CreditCommittee — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
       <c r="E39" s="31" t="inlineStr">
         <is>
-          <t>(SELECT MIN(E2.ENTRYDATE) FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee'))</t>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterChecker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="28" t="inlineStr">
         <is>
+          <t>PHV_USER</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên viên Thẩm định điện thoại</t>
+        </is>
+      </c>
+      <c r="D40" s="54" t="inlineStr">
+        <is>
+          <t>User xử lý bước PhoneVerification, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'PhoneVerification' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>APPROVER_USER</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên gia phê duyệt</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>User xử lý bước CreditApproval, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'CreditApproval' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>PROCESSED_DATE</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>Ngày xử lý hồ sơ</t>
+        </is>
+      </c>
+      <c r="D42" s="54" t="inlineStr">
+        <is>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.PROCESSED_DATE</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>A.PROCESSED_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Ngày khởi tạo hồ sơ</t>
+        </is>
+      </c>
+      <c r="D43" s="54" t="inlineStr">
+        <is>
+          <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CREATION_DATE</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>A.CREATION_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>LAST_APPROVAL_DATE</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D44" s="54" t="inlineStr">
+        <is>
+          <t>MAX(EXITDATE) tại bước phê duyệt (nhóm quyết định đã định nghĩa) — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>N1.LAST_APPROVAL_DATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>MIN_UWM</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian hồ sơ lên CV thẩm định</t>
+        </is>
+      </c>
+      <c r="D45" s="54" t="inlineStr">
+        <is>
+          <t>MIN(ENTRYDATE) tại UnderwriterMaker — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>N2.MIN_UWM</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>MIN_APP</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian hồ sơ lên CG phê duyệt</t>
+        </is>
+      </c>
+      <c r="D46" s="54" t="inlineStr">
+        <is>
+          <t>MIN(ENTRYDATE) tại CreditApproval/CreditCommittee — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>N3.MIN_APP</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
           <t>CANCEL_USER_DATE</t>
         </is>
       </c>
-      <c r="B40" s="25" t="inlineStr">
+      <c r="B47" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C40" s="26" t="inlineStr">
-        <is>
-          <t>Ngày hủy hồ sơ (có user)</t>
-        </is>
-      </c>
-      <c r="D40" s="54" t="inlineStr">
-        <is>
-          <t>EXITDATE tại bản ghi DECISION='Cancel' và USERNAME khác NULL — PHÁI SINH TẠI PDTD_DTM. DECISION_CODE tra qua WORKSTEP_DECISION_SK → STG_DIM_RLOS_WORKSTEP_DECISION</t>
-        </is>
-      </c>
-      <c r="E40" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.EXITDATE FROM E2 LEFT JOIN F ON F.DIMENSION_KEY = E2.WORKSTEP_DECISION_SK WHERE E2.WI_NAME = A.WI_NAME AND F.DECISION_CODE = 'Cancel' AND E2.USERNAME IS NOT NULL)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian cancel do NSD</t>
+        </is>
+      </c>
+      <c r="D47" s="54" t="inlineStr">
+        <is>
+          <t>EXITDATE tại bản ghi DECISION='Cancel' và USERNAME khác NULL — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.EXITDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE LEFT JOIN F WD ON WD.DIMENSION_KEY = WE.WORKSTEP_DECISION_SK WHERE WE.WI_NAME = A.WI_NAME AND WD.DECISION_CODE = 'Cancel' AND WE.USERNAME IS NOT NULL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="45" customHeight="1">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>CANCEL_DATE</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B48" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
-        <is>
-          <t>Ngày hủy hồ sơ</t>
-        </is>
-      </c>
-      <c r="D41" s="54" t="inlineStr">
-        <is>
-          <t>ENTRYDATE tại bước CancelRevoke — PHÁI SINH TẠI PDTD_DTM. FLAG_AUTO_CANCEL dùng cột này làm input</t>
-        </is>
-      </c>
-      <c r="E41" s="31" t="inlineStr">
-        <is>
-          <t>E2.ENTRYDATE WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'CancelRevoke'</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="45" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian vào vùng CancelRevoke</t>
+        </is>
+      </c>
+      <c r="D48" s="54" t="inlineStr">
+        <is>
+          <t>ENTRYDATE tại bước CancelRevoke — PHÁI SINH TẠI PDTD_DTM. FLAG_AUTO_CANCEL (business rule dựa trên cột này) tiếp tục tính tại chính bảng này, nay dùng input từ cột đã derive cùng bảng</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>N4.ENTRYDATE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>LAST_ENTRYDATE</t>
         </is>
       </c>
-      <c r="B42" s="25" t="inlineStr">
+      <c r="B49" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm vào bước gần nhất</t>
-        </is>
-      </c>
-      <c r="D42" s="54" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian vào bước cuối</t>
+        </is>
+      </c>
+      <c r="D49" s="54" t="inlineStr">
         <is>
           <t>ENTRYDATE của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E42" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.ENTRYDATE FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.EXITDATE IS NOT NULL AND E2.ENTRYDATE &lt;= v_batch_date ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.ENTRYDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="28" t="inlineStr">
         <is>
           <t>LAST_EXITDATE</t>
         </is>
       </c>
-      <c r="B43" s="25" t="inlineStr">
+      <c r="B50" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C43" s="26" t="inlineStr">
-        <is>
-          <t>Thời điểm thoát bước gần nhất</t>
-        </is>
-      </c>
-      <c r="D43" s="54" t="inlineStr">
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian kết thúc bước cuối</t>
+        </is>
+      </c>
+      <c r="D50" s="54" t="inlineStr">
         <is>
           <t>EXITDATE của cùng sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E43" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.EXITDATE FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.EXITDATE IS NOT NULL AND E2.ENTRYDATE &lt;= v_batch_date ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="60" customHeight="1">
-      <c r="A44" s="28" t="inlineStr">
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.EXITDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
         <is>
           <t>PRE_WORKSTEP_CODE</t>
         </is>
       </c>
-      <c r="B44" s="25" t="inlineStr">
+      <c r="B51" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>Bước xử lý liền trước</t>
-        </is>
-      </c>
-      <c r="D44" s="54" t="inlineStr">
-        <is>
-          <t>Bước xử lý liền trước (LAG theo ENTRYDATE) của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E44" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT LAG(E2.WORKSTEP_CODE) OVER (PARTITION BY E2.WI_NAME ORDER BY E2.ENTRYDATE) FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.EXITDATE IS NOT NULL AND E2.ENTRYDATE &lt;= v_batch_date ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
-      <c r="A45" s="28" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Bước hồ sơ trước đó</t>
+        </is>
+      </c>
+      <c r="D51" s="54" t="inlineStr">
+        <is>
+          <t>Bước xử lý liền trước (LAG theo ENTRYDATE) — PHÁI SINH TẠI PDTD_DTM, của sự kiện hoàn tất gần nhất</t>
+        </is>
+      </c>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>LAG(E.WORKSTEP_CODE) OVER (PARTITION BY E.WI_NAME ORDER BY E.ENTRYDATE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>LAST_REMARKS</t>
         </is>
       </c>
-      <c r="B45" s="25" t="inlineStr">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C45" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú bước gần nhất</t>
-        </is>
-      </c>
-      <c r="D45" s="54" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú ý kiến bước cuối</t>
+        </is>
+      </c>
+      <c r="D52" s="54" t="inlineStr">
         <is>
           <t>Ghi chú của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E45" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.REMARKS FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.EXITDATE IS NOT NULL AND E2.ENTRYDATE &lt;= v_batch_date ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="28" t="inlineStr">
         <is>
           <t>LAST_REMARK_DDE</t>
         </is>
       </c>
-      <c r="B46" s="25" t="inlineStr">
+      <c r="B53" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú bước DetailDataEntry</t>
-        </is>
-      </c>
-      <c r="D46" s="54" t="inlineStr">
+      <c r="C53" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú tại bước DDE</t>
+        </is>
+      </c>
+      <c r="D53" s="54" t="inlineStr">
         <is>
           <t>Ghi chú tại bước DetailDataEntry — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E46" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.REMARKS FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'DetailDataEntry' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="28" t="inlineStr">
+      <c r="E53" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DetailDataEntry' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
         <is>
           <t>LAST_CAN_REMARKS</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B54" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú lần hủy</t>
-        </is>
-      </c>
-      <c r="D47" s="54" t="inlineStr">
-        <is>
-          <t>Ghi chú tại lần hủy hồ sơ gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E47" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.REMARKS FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'CancelRevoke' AND E2.EXITDATE &lt;= v_batch_date ORDER BY E2.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="28" t="inlineStr">
-        <is>
-          <t>APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-      <c r="B48" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(25,2)</t>
-        </is>
-      </c>
-      <c r="C48" s="26" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối cùng</t>
-        </is>
-      </c>
-      <c r="D48" s="54" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối cùng — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-      <c r="E48" s="31" t="inlineStr">
-        <is>
-          <t>A.APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>APPROVED_TERM</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(15)</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>Kỳ hạn phê duyệt</t>
-        </is>
-      </c>
-      <c r="D49" s="54" t="inlineStr">
-        <is>
-          <t>Kỳ hạn phê duyệt — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_TERM</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
-        <is>
-          <t>A.APPROVED_TERM</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>CURRENCY_CODE</t>
-        </is>
-      </c>
-      <c r="B50" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(10)</t>
-        </is>
-      </c>
-      <c r="C50" s="26" t="inlineStr">
-        <is>
-          <t>Loại tiền</t>
-        </is>
-      </c>
-      <c r="D50" s="54" t="inlineStr">
-        <is>
-          <t>Loại tiền (BC3.CURRENCY) — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CURRENCY_CODE</t>
-        </is>
-      </c>
-      <c r="E50" s="31" t="inlineStr">
-        <is>
-          <t>A.CURRENCY_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERMAKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B51" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C51" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước UnderwriterMaker</t>
-        </is>
-      </c>
-      <c r="D51" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E51" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.UNDERWRITERMAKER_USERMAKE FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterMaker' ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="45" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERCHECKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước UnderwriterChecker</t>
-        </is>
-      </c>
-      <c r="D52" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.UNDERWRITERCHECKER_USERMAKE FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterChecker' ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="45" customHeight="1">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>APPROVAL_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B53" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C53" s="26" t="inlineStr">
-        <is>
-          <t>User làm bước phê duyệt</t>
-        </is>
-      </c>
-      <c r="D53" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E53" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT E2.APPROVAL_USERMAKE FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE IN ('CreditCommittee','CreditApproval') ORDER BY E2.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>CHANGE_REQUEST</t>
-        </is>
-      </c>
-      <c r="B54" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
       <c r="C54" s="26" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
+          <t>Ghi chú tại bước Cancel</t>
         </is>
       </c>
       <c r="D54" s="54" t="inlineStr">
         <is>
-          <t>Yêu cầu điều chỉnh hồ sơ — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_REQUEST</t>
+          <t>Ghi chú tại lần hủy hồ sơ — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E54" s="31" t="inlineStr">
         <is>
-          <t>A.CHANGE_REQUEST</t>
+          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'CancelRevoke' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="28" t="inlineStr">
         <is>
+          <t>APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(25,2)</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối</t>
+        </is>
+      </c>
+      <c r="D55" s="54" t="inlineStr">
+        <is>
+          <t>Hạn mức phê duyệt cuối cùng — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>A.APPROVED_AMT_FINAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(15)</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="D56" s="54" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="E56" s="31" t="inlineStr">
+        <is>
+          <t>A.APPROVED_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>CURRENCY_CODE</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>Loại tiền</t>
+        </is>
+      </c>
+      <c r="D57" s="54" t="inlineStr">
+        <is>
+          <t>Loại tiền (BC3.CURRENCY) — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CURRENCY_CODE</t>
+        </is>
+      </c>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>A.CURRENCY_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>UNDERWRITERMAKER_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="inlineStr">
+        <is>
+          <t>User Maker CVTĐ</t>
+        </is>
+      </c>
+      <c r="D58" s="54" t="inlineStr">
+        <is>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
+        </is>
+      </c>
+      <c r="E58" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.UNDERWRITERMAKER_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterMaker' ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>UNDERWRITERCHECKER_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="inlineStr">
+        <is>
+          <t>User Checker CVTĐ</t>
+        </is>
+      </c>
+      <c r="D59" s="54" t="inlineStr">
+        <is>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
+        </is>
+      </c>
+      <c r="E59" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.UNDERWRITERCHECKER_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterChecker' ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>APPROVAL_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>User Maker phê duyệt</t>
+        </is>
+      </c>
+      <c r="D60" s="54" t="inlineStr">
+        <is>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
+        </is>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.APPROVAL_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE IN ('CreditCommittee','CreditApproval') ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="D61" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_REQUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B55" s="25" t="inlineStr">
+      <c r="B62" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>Loại thay đổi điều kiện phê duyệt</t>
-        </is>
-      </c>
-      <c r="D55" s="54" t="inlineStr">
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>Loại thay đổi điều kiện</t>
+        </is>
+      </c>
+      <c r="D62" s="54" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện phê duyệt — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="E55" s="31" t="inlineStr">
+      <c r="E62" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="75" customHeight="1">
-      <c r="A56" s="28" t="inlineStr">
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_STATUS</t>
         </is>
       </c>
-      <c r="B56" s="25" t="inlineStr">
+      <c r="B63" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C56" s="26" t="inlineStr">
-        <is>
-          <t>Trạng thái hồ sơ chuẩn hóa</t>
-        </is>
-      </c>
-      <c r="D56" s="54" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
+        <is>
+          <t>Trạng thái hồ sơ</t>
+        </is>
+      </c>
+      <c r="D63" s="54" t="inlineStr">
         <is>
           <t>Trạng thái hồ sơ chuẩn hóa (BC1) — PHÁI SINH TẠI PDTD_DTM, business rule (đồng bộ theo pattern CLOS)</t>
         </is>
       </c>
-      <c r="E56" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F ON F.DIMENSION_KEY = A.WORKSTEP_DECISION_SK → CASE WHEN F.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport') THEN 'Approved' WHEN F.DECISION_CODE = 'Reject' THEN 'Rejected' WHEN F.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent') THEN 'Cancelled' ELSE 'Processing' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="165" customHeight="1">
-      <c r="A57" s="28" t="inlineStr">
+      <c r="E63" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN F.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport') THEN 'Approved' WHEN F.DECISION_CODE = 'Reject' THEN 'Rejected' WHEN F.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent') THEN 'Cancelled' ELSE 'Processing' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="180" customHeight="1">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>AUTO_CANCEL_DATE</t>
         </is>
       </c>
-      <c r="B57" s="25" t="inlineStr">
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
-        <is>
-          <t>Ngày tự động hủy hồ sơ</t>
-        </is>
-      </c>
-      <c r="D57" s="54" t="inlineStr">
-        <is>
-          <t>Ngày hồ sơ bị hệ thống tự động chuyển sang CancelRevoke (BC1.AUTO_CAN_DATE) — PHÁI SINH TẠI PDTD_DTM.</t>
-        </is>
-      </c>
-      <c r="E57" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT MIN(E2.ENTRYDATE) FROM E2 LEFT JOIN F ON F.DIMENSION_KEY = E2.WORKSTEP_DECISION_SK WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'CancelRevoke' AND ( (E2.USERNAME IS NULL AND E2.EXITDATE IS NULL AND F.DECISION_CODE IS NULL) OR (E2.EXITDATE IS NULL AND F.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM E2 BS WHERE BS.WI_NAME = E2.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E2.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E2.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM E2 C2 LEFT JOIN F FC ON FC.DIMENSION_KEY = C2.WORKSTEP_DECISION_SK WHERE C2.WI_NAME = E2.WI_NAME AND FC.DECISION_CODE = 'Cancel' AND C2.ENTRYDATE &lt;= E2.ENTRYDATE))</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="165" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian cancel tự động</t>
+        </is>
+      </c>
+      <c r="D64" s="54" t="inlineStr">
+        <is>
+          <t>Ngày hồ sơ bị hệ thống tự động chuyển sang CancelRevoke (BC1.AUTO_CAN_DATE) — PHÁI SINH TẠI PDTD_DTM. MIN(ENTRYDATE) tại CancelRevoke thỏa 1 trong 2 nhánh — (1) dòng đang mở hoàn toàn, (2) từng treo tại BranchSupport ≥2400 phút nghiệp vụ (GET_BUSINESS_MINUTE) trước khi vào CancelRevoke — loại trừ hồ sơ có bước hủy thủ công (DECISION_CODE='Cancel') trước/cùng thời điểm.</t>
+        </is>
+      </c>
+      <c r="E64" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT MIN(E.ENTRYDATE) FROM STG_FCT_RLOS_WORKSTEP_EVENT E LEFT JOIN F WD ON WD.DIMENSION_KEY = E.WORKSTEP_DECISION_SK WHERE E.WI_NAME = A.WI_NAME AND E.WORKSTEP_CODE = 'CancelRevoke' AND ( (E.USERNAME IS NULL AND E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL) OR (E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT BS WHERE BS.WI_NAME = E.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT C LEFT JOIN STG_DIM_RLOS_WORKSTEP_DECISION WDC ON WDC.DIMENSION_KEY = C.WORKSTEP_DECISION_SK WHERE C.WI_NAME = E.WI_NAME AND WDC.DECISION_CODE = 'Cancel' AND C.ENTRYDATE &lt;= E.ENTRYDATE))</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="195" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>FLAG_AUTO_CANCEL</t>
         </is>
       </c>
-      <c r="B58" s="25" t="inlineStr">
+      <c r="B65" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>Cờ tự động hủy</t>
-        </is>
-      </c>
-      <c r="D58" s="54" t="inlineStr">
-        <is>
-          <t>'YES'/'NO' theo nguyên văn SRS BC1 field FLAG_AUTO_CAN — PHÁI SINH TẠI PDTD_DTM, cùng tập điều kiện EXISTS như AUTO_CANCEL_DATE (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E58" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN EXISTS (SELECT 1 FROM E2 LEFT JOIN F ON F.DIMENSION_KEY = E2.WORKSTEP_DECISION_SK WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'CancelRevoke' AND ( (E2.USERNAME IS NULL AND E2.EXITDATE IS NULL AND F.DECISION_CODE IS NULL) OR (E2.EXITDATE IS NULL AND F.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM E2 BS WHERE BS.WI_NAME = E2.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E2.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E2.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM E2 C2 LEFT JOIN F FC ON FC.DIMENSION_KEY = C2.WORKSTEP_DECISION_SK WHERE C2.WI_NAME = E2.WI_NAME AND FC.DECISION_CODE = 'Cancel' AND C2.ENTRYDATE &lt;= E2.ENTRYDATE)) THEN 'YES' ELSE 'NO' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="105" customHeight="1">
-      <c r="A59" s="28" t="inlineStr">
+      <c r="C65" s="26" t="inlineStr">
+        <is>
+          <t>Hồ sơ cancel tự động</t>
+        </is>
+      </c>
+      <c r="D65" s="54" t="inlineStr">
+        <is>
+          <t>'YES'/'NO' theo nguyên văn SRS BC1 field FLAG_AUTO_CAN (BC1) — PHÁI SINH TẠI PDTD_DTM. YES nếu tồn tại dòng CancelRevoke thỏa cùng điều kiện Auto-Cancel đã mô tả ở AUTO_CANCEL_DATE.</t>
+        </is>
+      </c>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT E LEFT JOIN F WD ON WD.DIMENSION_KEY = E.WORKSTEP_DECISION_SK WHERE E.WI_NAME = A.WI_NAME AND E.WORKSTEP_CODE = 'CancelRevoke' AND ( (E.USERNAME IS NULL AND E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL) OR (E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT BS WHERE BS.WI_NAME = E.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT C LEFT JOIN STG_DIM_RLOS_WORKSTEP_DECISION WDC ON WDC.DIMENSION_KEY = C.WORKSTEP_DECISION_SK WHERE C.WI_NAME = E.WI_NAME AND WDC.DECISION_CODE = 'Cancel' AND C.ENTRYDATE &lt;= E.ENTRYDATE)) THEN 'YES' ELSE 'NO' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="60" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>LAST_WORKSTEP</t>
         </is>
       </c>
-      <c r="B59" s="25" t="inlineStr">
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C59" s="26" t="inlineStr">
-        <is>
-          <t>Tên bước hoàn tất gần nhất</t>
-        </is>
-      </c>
-      <c r="D59" s="54" t="inlineStr">
-        <is>
-          <t>Tên bước hoàn tất gần nhất, chuẩn hóa dùng chung 2 hệ...' ở điều kiện JOIN (không spell-out đầy đủ) — tái tạo theo đúng pattern đã dùng cho FCT_CLOS_APPLICATION.LAST_WORKSTEP (JOIN qua WORKSTEP_DECISION_SK rồi WORKSTEP_CODE/DECISION_CODE sang Q_RLOS_REF_WORKSTEP_2SYSTEMS), cần user xác nhận đúng ý định</t>
-        </is>
-      </c>
-      <c r="E59" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F ON F.DIMENSION_KEY = A.WORKSTEP_DECISION_SK → LEFT JOIN G ON G.WORKSTEP_CODE = F.WORKSTEP_CODE AND G.DECISION_CODE = F.DECISION_CODE → G.WORKSTEP_NAME_STD</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="28" t="inlineStr">
+      <c r="C66" s="26" t="inlineStr">
+        <is>
+          <t>Bước hồ sơ cuối cùng</t>
+        </is>
+      </c>
+      <c r="D66" s="54" t="inlineStr">
+        <is>
+          <t>Tên bước hoàn tất gần nhất, chuẩn hóa dùng chung 2 hệ. [CẦN REVIEW] etl_logic gốc chỉ viết '...' không spell rõ điều kiện JOIN đầy đủ (note nhắc hop qua WORKSTEP_DECISION_SK, cùng pattern CLOS) — cần xác nhận lại chuỗi JOIN đầy đủ.</t>
+        </is>
+      </c>
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>G.WORKSTEP_NAME_STD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>BUSINESS_FLOW</t>
         </is>
       </c>
-      <c r="B60" s="25" t="inlineStr">
+      <c r="B67" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
-        <is>
-          <t>Luồng nghiệp vụ chuẩn hóa</t>
-        </is>
-      </c>
-      <c r="D60" s="54" t="inlineStr">
+      <c r="C67" s="26" t="inlineStr">
+        <is>
+          <t>Phân khúc hồ sơ</t>
+        </is>
+      </c>
+      <c r="D67" s="54" t="inlineStr">
         <is>
           <t>Luồng nghiệp vụ chuẩn hóa để hiển thị trên báo cáo</t>
         </is>
       </c>
-      <c r="E60" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C ON C.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN H ON H.STREAM = C.STREAM → H.BUSINESS_FLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="28" t="inlineStr">
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>H.BUSINESS_FLOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>DEVIATION_G3</t>
         </is>
       </c>
-      <c r="B61" s="25" t="inlineStr">
+      <c r="B68" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C61" s="26" t="inlineStr">
-        <is>
-          <t>Cờ ≥3 ngoại lệ chính sách</t>
-        </is>
-      </c>
-      <c r="D61" s="54" t="inlineStr">
-        <is>
-          <t>Hồ sơ có từ 3 ngoại lệ chính sách trở lên hay không (YES/NO) — CHUYỂN TỪ DIM_RLOS_APPLICATION. Report-time: DAYID=MAX(DAYID)/WI_NAME, COUNT(*)&gt;=3 → YES</t>
-        </is>
-      </c>
-      <c r="E61" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN (SELECT COUNT(*) FROM I WHERE I.WI_NAME = A.WI_NAME AND I.DAYID = (SELECT MAX(DAYID) FROM I WHERE WI_NAME = A.WI_NAME)) &gt;= 3 THEN 'YES' ELSE 'NO' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="90" customHeight="1">
-      <c r="A62" s="28" t="inlineStr">
+      <c r="C68" s="26" t="inlineStr">
+        <is>
+          <t>Hồ sơ có từ 3 ngoại lệ</t>
+        </is>
+      </c>
+      <c r="D68" s="54" t="inlineStr">
+        <is>
+          <t>Hồ sơ có từ 3 ngoại lệ chính sách trở lên hay không (YES/NO) — CHUYỂN TỪ DIM_RLOS_APPLICATION</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN (SELECT COUNT(*) FROM STG_FCT_RLOS_DEVIATION DV WHERE DV.WI_NAME = A.WI_NAME AND DV.DAYID = (SELECT MAX(DAYID) FROM STG_FCT_RLOS_DEVIATION WHERE WI_NAME = A.WI_NAME)) &gt;= 3 THEN 'YES' ELSE 'NO' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>REF_PRODUCT</t>
         </is>
       </c>
-      <c r="B62" s="25" t="inlineStr">
+      <c r="B69" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="C69" s="26" t="inlineStr">
         <is>
           <t>Nhóm sản phẩm tra SLA</t>
         </is>
       </c>
-      <c r="D62" s="54" t="inlineStr">
-        <is>
-          <t>Nhóm sản phẩm dùng để tra cam kết SLA (BC5) — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM. either/or theo PRODUCTLINE_NAME hoặc CHANGE_TYPE (chỉ so khớp CHANGE_TYPE khi dòng REF_ có PRODUCT_LINE='Trường Change Request')</t>
-        </is>
-      </c>
-      <c r="E62" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN K ON K.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK → LEFT JOIN C ON C.DIMENSION_KEY = A.APPLICATION_SK → LEFT JOIN J ON (J.PRODUCT_LINE = K.PRODUCTLINE_NAME OR (J.PRODUCT_LINE = 'Trường Change Request' AND J.PRODUCT_LINE = A.CHANGE_TYPE)) AND J.DEVIATION_G3 = A.DEVIATION_G3 AND J.SECONDARY_PRODUCTLINE = C.IS_SEC_PRODUCT AND J.APP_GRP = C.APP_GRP → J.REF_PRODUCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="28" t="inlineStr">
+      <c r="D69" s="54" t="inlineStr">
+        <is>
+          <t>Nhóm sản phẩm dùng để tra cam kết SLA (BC5) — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM. either/or theo PRODUCTLINE_NAME hoặc CHANGE_TYPE.</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>K.REF_PRODUCT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>SLA_CREDIT_OFFICER</t>
         </is>
       </c>
-      <c r="B63" s="25" t="inlineStr">
+      <c r="B70" s="25" t="inlineStr">
         <is>
           <t>NUMBER(10,2)</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ chuyên viên tín dụng</t>
-        </is>
-      </c>
-      <c r="D63" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho chuyên viên tín dụng — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E63" s="31" t="inlineStr">
-        <is>
-          <t>J.SLA_CREDIT_OFFICER</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
+      <c r="C70" s="26" t="inlineStr">
+        <is>
+          <t>Cam kết SLA chuyên viên tín dụng</t>
+        </is>
+      </c>
+      <c r="D70" s="54" t="inlineStr">
+        <is>
+          <t>Cam kết giờ cho chuyên viên tín dụng — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>K.SLA_CREDIT_OFFICER</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="45" customHeight="1">
+      <c r="A71" s="28" t="inlineStr">
         <is>
           <t>SLA_MARKER</t>
         </is>
       </c>
-      <c r="B64" s="25" t="inlineStr">
+      <c r="B71" s="25" t="inlineStr">
         <is>
           <t>NUMBER(10,2)</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ lập hồ sơ thẩm định</t>
-        </is>
-      </c>
-      <c r="D64" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho bước lập hồ sơ thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E64" s="31" t="inlineStr">
-        <is>
-          <t>J.SLA_MARKER</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
-      <c r="A65" s="28" t="inlineStr">
+      <c r="C71" s="26" t="inlineStr">
+        <is>
+          <t>Cam kết SLA lập hồ sơ thẩm định</t>
+        </is>
+      </c>
+      <c r="D71" s="54" t="inlineStr">
+        <is>
+          <t>Cam kết giờ cho bước lập hồ sơ thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>K.SLA_MARKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="45" customHeight="1">
+      <c r="A72" s="28" t="inlineStr">
         <is>
           <t>SLA_CHECKER</t>
         </is>
       </c>
-      <c r="B65" s="25" t="inlineStr">
+      <c r="B72" s="25" t="inlineStr">
         <is>
           <t>NUMBER(10,2)</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ kiểm soát thẩm định</t>
-        </is>
-      </c>
-      <c r="D65" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho bước kiểm soát thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E65" s="31" t="inlineStr">
-        <is>
-          <t>J.SLA_CHECKER</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
+      <c r="C72" s="26" t="inlineStr">
+        <is>
+          <t>Cam kết SLA kiểm soát thẩm định</t>
+        </is>
+      </c>
+      <c r="D72" s="54" t="inlineStr">
+        <is>
+          <t>Cam kết giờ cho bước kiểm soát thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>K.SLA_CHECKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="45" customHeight="1">
+      <c r="A73" s="28" t="inlineStr">
         <is>
           <t>SLA_CREDIT_APPROVER</t>
         </is>
       </c>
-      <c r="B66" s="25" t="inlineStr">
+      <c r="B73" s="25" t="inlineStr">
         <is>
           <t>NUMBER(10,2)</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cấp phê duyệt</t>
-        </is>
-      </c>
-      <c r="D66" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho cấp phê duyệt — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng JOIN với REF_PRODUCT (cột cùng bảng)</t>
-        </is>
-      </c>
-      <c r="E66" s="31" t="inlineStr">
-        <is>
-          <t>J.SLA_CREDIT_APPROVER</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="105" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>Cam kết SLA cấp phê duyệt</t>
+        </is>
+      </c>
+      <c r="D73" s="54" t="inlineStr">
+        <is>
+          <t>Cam kết giờ cho cấp phê duyệt — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>K.SLA_CREDIT_APPROVER</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="75" customHeight="1">
+      <c r="A74" s="28" t="inlineStr">
         <is>
           <t>HAS_DDE_FLAG</t>
         </is>
       </c>
-      <c r="B67" s="25" t="inlineStr">
+      <c r="B74" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
+      <c r="C74" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới DetailDataEntry</t>
         </is>
       </c>
-      <c r="D67" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước DetailDataEntry', chỉ chuyển Y, không bao giờ quay lại N. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION) thay cho EXISTS quét lịch sử WORKSTEP_EVENT. Carry-forward từ FCT_RLOS_APPLICATION_PREV (snapshot DAYID=v_batch_date-1, TRUNCATE+INSERT trước khi chạy batch) OR event mới trong batch hiện tại</t>
-        </is>
-      </c>
-      <c r="E67" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(L.HAS_DDE_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'DetailDataEntry') THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="75" customHeight="1">
-      <c r="A68" s="28" t="inlineStr">
+      <c r="D74" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước DetailDataEntry', chỉ chuyển Y, không bao giờ quay lại N. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION) thay cho EXISTS quét lịch sử WORKSTEP_EVENT. Cùng cơ chế đã áp dụng cho FCT_CLOS_APPLICATION.</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_DDE_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'DetailDataEntry') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>HAS_UWM_FLAG</t>
         </is>
       </c>
-      <c r="B68" s="25" t="inlineStr">
+      <c r="B75" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="C75" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới UnderwriterMaker</t>
         </is>
       </c>
-      <c r="D68" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterMaker'. Dùng cho carry-forward hồ sơ treo trên FCT_RLOS_WORKSTEP_EVENT (lọc phạm vi BC4) và nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION). Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E68" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(L.HAS_UWM_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterMaker') THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="60" customHeight="1">
-      <c r="A69" s="28" t="inlineStr">
+      <c r="D75" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterMaker'. Dùng cho carry-forward hồ sơ treo trên FCT_RLOS_WORKSTEP_EVENT (lọc phạm vi BC4) và nguồn cho VOLUME</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_UWM_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterMaker') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>HAS_UWC_FLAG</t>
         </is>
       </c>
-      <c r="B69" s="25" t="inlineStr">
+      <c r="B76" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C69" s="26" t="inlineStr">
+      <c r="C76" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới UnderwriterChecker</t>
         </is>
       </c>
-      <c r="D69" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterChecker'. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION, mức 0.6). Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E69" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(L.HAS_UWC_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE = 'UnderwriterChecker') THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="28" t="inlineStr">
+      <c r="D76" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterChecker'. Nguồn cho VOLUME (mức 0.6)</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_UWC_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterChecker') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="28" t="inlineStr">
         <is>
           <t>HAS_APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B70" s="25" t="inlineStr">
+      <c r="B77" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã tới bước phê duyệt</t>
-        </is>
-      </c>
-      <c r="D70" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước CreditApproval/CreditCommittee' (chưa cần đã có quyết định). Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION, mức 0.8). Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(L.HAS_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee')) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="105" customHeight="1">
-      <c r="A71" s="28" t="inlineStr">
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã tới cấp phê duyệt</t>
+        </is>
+      </c>
+      <c r="D77" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước CreditApproval/CreditCommittee' (chưa cần đã có quyết định). Nguồn cho VOLUME (mức 0.8)</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee')) THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="90" customHeight="1">
+      <c r="A78" s="28" t="inlineStr">
         <is>
           <t>HAS_FINAL_APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B71" s="25" t="inlineStr">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C71" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã có quyết định phê duyệt hoàn tất</t>
-        </is>
-      </c>
-      <c r="D71" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã có quyết định phê duyệt hoàn tất' (case 1 của PROCESSED_DATE). Nguồn cho VOLUME mức 1.0 và điều kiện loại khỏi carry-forward hồ sơ treo. Cùng cơ chế carry-forward với HAS_DDE_FLAG, nhưng EXISTS cần JOIN thêm STG_DIM_RLOS_WORKSTEP_DECISION để lấy DECISION_CODE</t>
-        </is>
-      </c>
-      <c r="E71" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(L.HAS_FINAL_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM E2 JOIN F ON F.DIMENSION_KEY = E2.WORKSTEP_DECISION_SK WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND F.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport','Reject')) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="60" customHeight="1">
-      <c r="A72" s="28" t="inlineStr">
+      <c r="C78" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã có quyết định phê duyệt</t>
+        </is>
+      </c>
+      <c r="D78" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã có quyết định phê duyệt hoàn tất' (case 1 của PROCESSED_DATE). Nguồn cho VOLUME mức 1.0</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_FINAL_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e JOIN F wd ON wd.DIMENSION_KEY = e.WORKSTEP_DECISION_SK WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND wd.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport','Reject')) THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>HAS_CANCELLED_FLAG</t>
         </is>
       </c>
-      <c r="B72" s="25" t="inlineStr">
+      <c r="B79" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C72" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã hủy hồ sơ</t>
-        </is>
-      </c>
-      <c r="D72" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã rơi vào CancelRevoke/CancelPermanent'. VOLUME dùng cờ này để xác nhận hồ sơ đã KẾT THÚC do hủy — khi đó lấy điểm theo bước xa nhất đã đạt thay vì NULL. Cùng cơ chế carry-forward với HAS_DDE_FLAG</t>
-        </is>
-      </c>
-      <c r="E72" s="31" t="inlineStr">
-        <is>
-          <t>LEFT JOIN L ON L.WI_NAME = A.WI_NAME → CASE WHEN COALESCE(L.HAS_CANCELLED_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM E2 WHERE E2.WI_NAME = A.WI_NAME AND E2.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent')) THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="55" t="inlineStr">
-        <is>
-          <t>Chú ý:</t>
-        </is>
-      </c>
-      <c r="B75" s="55" t="inlineStr">
-        <is>
-          <t>1. FCT_RLOS_APPLICATION_PREV (alias L) là snapshot DAYID=v_batch_date-1 của chính bảng FCT_RLOS_APPLICATION — phải TRUNCATE+INSERT bảng _PREV này TRƯỚC khi chạy batch ghi FCT_RLOS_APPLICATION, để tránh vừa đọc vừa ghi trên cùng bảng đích. Cùng cơ chế carry-forward đã áp dụng cho FCT_CLOS_APPLICATION.</t>
+      <c r="C79" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã bị hủy</t>
+        </is>
+      </c>
+      <c r="D79" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã rơi vào CancelRevoke/CancelPermanent'. VOLUME dùng cờ này để xác nhận hồ sơ đã KẾT THÚC do hủy, lấy điểm theo bước xa nhất đã đạt trước khi hủy thay vì NULL</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_CANCELLED_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent')) THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="10" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="55" t="inlineStr">
+        <is>
+          <t>Điều kiện join giữa các bảng</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="n"/>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="25" t="n"/>
+      <c r="B82" s="25" t="n"/>
+      <c r="C82" s="51" t="n"/>
+      <c r="D82" s="54" t="n"/>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.DIMENSION_KEY = A.APPLICATION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="25" t="n"/>
+      <c r="B83" s="25" t="n"/>
+      <c r="C83" s="51" t="n"/>
+      <c r="D83" s="54" t="n"/>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.MAIN_ID = C.RESULT_MAIN_CARD_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="25" t="n"/>
+      <c r="B84" s="25" t="n"/>
+      <c r="C84" s="51" t="n"/>
+      <c r="D84" s="54" t="n"/>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D.RECID = C.RESULT_MAIN_CARD_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="60" customHeight="1">
+      <c r="A85" s="25" t="n"/>
+      <c r="B85" s="25" t="n"/>
+      <c r="C85" s="51" t="n"/>
+      <c r="D85" s="54" t="n"/>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N1 (SELECT WI_NAME, MAX(EXITDATE) AS LAST_APPROVAL_DATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N1 ON N1.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="45" customHeight="1">
+      <c r="A86" s="25" t="n"/>
+      <c r="B86" s="25" t="n"/>
+      <c r="C86" s="51" t="n"/>
+      <c r="D86" s="54" t="n"/>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N2 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_UWM FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'UnderwriterMaker' GROUP BY WI_NAME) N2 ON N2.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="60" customHeight="1">
+      <c r="A87" s="25" t="n"/>
+      <c r="B87" s="25" t="n"/>
+      <c r="C87" s="51" t="n"/>
+      <c r="D87" s="54" t="n"/>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N3 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_APP FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N3 ON N3.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="45" customHeight="1">
+      <c r="A88" s="25" t="n"/>
+      <c r="B88" s="25" t="n"/>
+      <c r="C88" s="51" t="n"/>
+      <c r="D88" s="54" t="n"/>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN N4 (SELECT WI_NAME, ENTRYDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'CancelRevoke') N4 ON N4.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="25" t="n"/>
+      <c r="B89" s="25" t="n"/>
+      <c r="C89" s="51" t="n"/>
+      <c r="D89" s="54" t="n"/>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN F.DIMENSION_KEY = A.WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="25" t="n"/>
+      <c r="B90" s="25" t="n"/>
+      <c r="C90" s="51" t="n"/>
+      <c r="D90" s="54" t="n"/>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN G.WORKSTEP_CODE = F.WORKSTEP_CODE AND G.DECISION_CODE = F.DECISION_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="25" t="n"/>
+      <c r="B91" s="25" t="n"/>
+      <c r="C91" s="51" t="n"/>
+      <c r="D91" s="54" t="n"/>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN H.STREAM = C.STREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="25" t="n"/>
+      <c r="B92" s="25" t="n"/>
+      <c r="C92" s="51" t="n"/>
+      <c r="D92" s="54" t="n"/>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN J.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="75" customHeight="1">
+      <c r="A93" s="25" t="n"/>
+      <c r="B93" s="25" t="n"/>
+      <c r="C93" s="51" t="n"/>
+      <c r="D93" s="54" t="n"/>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN K ON (K.PRODUCT_LINE = J.PRODUCTLINE_NAME OR (K.PRODUCT_LINE = 'Trường Change Request' AND K.PRODUCT_LINE = A.CHANGE_TYPE)) AND K.DEVIATION_G3 = DEVIATION_G3 (cột cùng bảng) AND K.SECONDARY_PRODUCTLINE = C.IS_SEC_PRODUCT AND K.APP_GRP = C.APP_GRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="25" t="n"/>
+      <c r="B94" s="25" t="n"/>
+      <c r="C94" s="51" t="n"/>
+      <c r="D94" s="54" t="n"/>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN L.WI_NAME = A.WI_NAME</t>
         </is>
       </c>
     </row>

--- a/mapping/PDTD_DTM/Mapping_FCT_RLOS_APPLICATION.xlsx
+++ b/mapping/PDTD_DTM/Mapping_FCT_RLOS_APPLICATION.xlsx
@@ -718,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="D20" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. Mặc định -1 — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.WORKSTEP_DECISION_SK (đổi tên từ LAST_WORKSTEP_DECISION_SK)</t>
+          <t>Khóa tới DIM_RLOS_WORKSTEP_DECISION. Mặc định -1 — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.WORKSTEP_DECISION_SK (đổi tên từ LAST_WORKSTEP_DECISION_SK, đồng bộ pattern CLOS)</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
@@ -1070,7 +1070,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="60" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT_SK</t>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="D23" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product) — lookup theo PRODUCTLINE_CODE/SUB_PRODUCT_NAME, điều kiện SCD2 hiệu lực tại DAYID</t>
+          <t>Khóa tới DIM_RLOS_PRODUCT (layer Sub Product) — lookup theo PRODUCTLINE_CODE/SUB_PRODUCT_NAME, điều kiện SCD2 hiệu lực tại DAYID. Mặc định -1 nếu không khớp — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.SUB_PRODUCT_SK</t>
         </is>
       </c>
       <c r="E23" s="31" t="inlineStr">
@@ -1097,10 +1097,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
         <is>
-          <t>SUB_PRODUCT_CODE</t>
+          <t>PRODUCTLINE_CODE</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
@@ -1110,321 +1110,321 @@
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Mã sản phẩm nhánh</t>
+          <t>Mã dòng sản phẩm</t>
         </is>
       </c>
       <c r="D24" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK thật cạnh SK (layer Sub Product), giá trị đã có sẵn trong bước lookup SUB_PRODUCT_SK</t>
+          <t>CỘT MỚI (review 2026-10-27) — BK cạnh SK, nửa còn lại của cặp khóa lookup DIM_RLOS_PRODUCT (cùng SUB_PRODUCT_NAME) cần để tra SUB_PRODUCT_SK — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.PRODUCTLINE_CODE</t>
         </is>
       </c>
       <c r="E24" s="31" t="inlineStr">
         <is>
-          <t>A.SUB_PRODUCT_CODE</t>
+          <t>A.PRODUCTLINE_CODE</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_SK</t>
+          <t>SUB_PRODUCT_CODE</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Khóa đơn vị kinh doanh</t>
+          <t>Mã sản phẩm nhánh</t>
         </is>
       </c>
       <c r="D25" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_LOS_COMPANY — lookup theo COMPANY_CODE, điều kiện SCD2 hiệu lực tại DAYID. Mặc định -1 nếu không khớp</t>
+          <t>CỘT MỚI — BK thật cạnh SK (layer Sub Product), giá trị đã có sẵn trong bước lookup SUB_PRODUCT_SK</t>
         </is>
       </c>
       <c r="E25" s="31" t="inlineStr">
         <is>
-          <t>A.COMPANY_SK</t>
+          <t>A.SUB_PRODUCT_CODE</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="28" t="inlineStr">
         <is>
-          <t>COMPANY_CODE</t>
+          <t>COMPANY_SK</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Mã đơn vị kinh doanh</t>
+          <t>Khóa đơn vị kinh doanh</t>
         </is>
       </c>
       <c r="D26" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK (layer Company), cùng giá trị đã dùng để lookup COMPANY_SK</t>
+          <t>Khóa tới DIM_LOS_COMPANY — lookup theo COMPANY_CODE, điều kiện SCD2 hiệu lực tại DAYID. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E26" s="31" t="inlineStr">
         <is>
-          <t>A.COMPANY_CODE</t>
+          <t>A.COMPANY_SK</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
         <is>
+          <t>COMPANY_CODE</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(50)</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Mã đơn vị kinh doanh</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK (layer Company), cùng giá trị đã dùng để lookup COMPANY_SK</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>A.COMPANY_CODE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C27" s="26" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Khóa loại thay đổi</t>
         </is>
       </c>
-      <c r="D27" s="54" t="inlineStr">
+      <c r="D28" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_RLOS_CHANGE_TYPE. Chỉ có giá trị với hồ sơ thay đổi điều kiện phê duyệt, còn lại Unknown -1</t>
         </is>
       </c>
-      <c r="E27" s="31" t="inlineStr">
+      <c r="E28" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE_SK</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>CHANGE_TYPE_CODE</t>
         </is>
       </c>
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C28" s="26" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Mã loại thay đổi</t>
         </is>
       </c>
-      <c r="D28" s="54" t="inlineStr">
+      <c r="D29" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — BK cạnh SK, 1 phần BK composite (CHANGE_TYPE_CODE+DETAIL_CHANGE_TYPE_CODE) của DIM_RLOS_CHANGE_TYPE, giá trị đã có sẵn trong bước lookup CHANGE_TYPE_SK</t>
         </is>
       </c>
-      <c r="E28" s="31" t="inlineStr">
+      <c r="E29" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
-        <is>
-          <t>DETAIL_CHANGE_TYPE_CODE</t>
-        </is>
-      </c>
-      <c r="B29" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C29" s="26" t="inlineStr">
-        <is>
-          <t>Mã chi tiết loại thay đổi</t>
-        </is>
-      </c>
-      <c r="D29" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — nửa còn lại BK composite DIM_RLOS_CHANGE_TYPE, giá trị đã có sẵn trong bước lookup CHANGE_TYPE_SK</t>
-        </is>
-      </c>
-      <c r="E29" s="31" t="inlineStr">
-        <is>
-          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="28" t="inlineStr">
         <is>
-          <t>CARD_PROMOTION_SK</t>
+          <t>DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(100)</t>
         </is>
       </c>
       <c r="C30" s="26" t="inlineStr">
         <is>
-          <t>Khóa ưu đãi phí thẻ</t>
+          <t>Mã chi tiết loại thay đổi</t>
         </is>
       </c>
       <c r="D30" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Hồ sơ không phải thẻ dùng -1</t>
+          <t>CỘT MỚI — nửa còn lại BK composite DIM_RLOS_CHANGE_TYPE, giá trị đã có sẵn trong bước lookup CHANGE_TYPE_SK</t>
         </is>
       </c>
       <c r="E30" s="31" t="inlineStr">
         <is>
-          <t>A.CARD_PROMOTION_SK</t>
+          <t>A.DETAIL_CHANGE_TYPE_CODE</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="28" t="inlineStr">
         <is>
-          <t>PROMOTION_CODE</t>
+          <t>CARD_PROMOTION_SK</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(50)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C31" s="26" t="inlineStr">
         <is>
-          <t>Mã ưu đãi phí</t>
+          <t>Khóa ưu đãi phí thẻ</t>
         </is>
       </c>
       <c r="D31" s="54" t="inlineStr">
         <is>
-          <t>CỘT MỚI — BK cạnh SK, cùng giá trị đã dùng để lookup CARD_PROMOTION_SK</t>
+          <t>Khóa tới DIM_RLOS_CARD_PROMOTION. Hồ sơ không phải thẻ dùng -1</t>
         </is>
       </c>
       <c r="E31" s="31" t="inlineStr">
         <is>
-          <t>A.PROMOTION_CODE</t>
+          <t>A.CARD_PROMOTION_SK</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
-          <t>T24_CARD_SK</t>
+          <t>PROMOTION_CODE</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>NUMBER</t>
+          <t>VARCHAR2(50)</t>
         </is>
       </c>
       <c r="C32" s="26" t="inlineStr">
         <is>
-          <t>Khóa thẻ T24</t>
+          <t>Mã ưu đãi phí</t>
         </is>
       </c>
       <c r="D32" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_T24_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH</t>
+          <t>CỘT MỚI — BK cạnh SK, cùng giá trị đã dùng để lookup CARD_PROMOTION_SK</t>
         </is>
       </c>
       <c r="E32" s="31" t="inlineStr">
         <is>
-          <t>B.DIMENSION_KEY</t>
+          <t>A.PROMOTION_CODE</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="28" t="inlineStr">
         <is>
+          <t>T24_CARD_SK</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Khóa thẻ T24</t>
+        </is>
+      </c>
+      <c r="D33" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_T24_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>B.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
           <t>T24_SEAB_MAIN_CARD_SK</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B34" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C33" s="26" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Khóa thẻ chính SEAB</t>
         </is>
       </c>
-      <c r="D33" s="54" t="inlineStr">
+      <c r="D34" s="54" t="inlineStr">
         <is>
           <t>Khóa tới DIM_T24_SEAB_MAIN_CARD. Mặc định -1 — BỔ SUNG RIÊNG TẠI PDTD_DTM, không có ở SB_DWH</t>
         </is>
       </c>
-      <c r="E33" s="31" t="inlineStr">
+      <c r="E34" s="31" t="inlineStr">
         <is>
           <t>D.DIMENSION_KEY</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="60" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>USER_SK</t>
-        </is>
-      </c>
-      <c r="B34" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER</t>
-        </is>
-      </c>
-      <c r="C34" s="26" t="inlineStr">
-        <is>
-          <t>Khóa người xử lý</t>
-        </is>
-      </c>
-      <c r="D34" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_LOS_USER của người xử lý sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT WE.USER_SK FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
-          <t>BRANCH_USER</t>
+          <t>USER_SK</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>VARCHAR2(100)</t>
+          <t>NUMBER</t>
         </is>
       </c>
       <c r="C35" s="26" t="inlineStr">
         <is>
-          <t>User Chi nhánh</t>
+          <t>Khóa người xử lý</t>
         </is>
       </c>
       <c r="D35" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước BranchSupport, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>Khóa tới DIM_LOS_USER của người xử lý sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E35" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'BranchSupport' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.USER_SK FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="36" ht="60" customHeight="1">
       <c r="A36" s="28" t="inlineStr">
         <is>
-          <t>DDE_USER</t>
+          <t>BRANCH_USER</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
@@ -1434,24 +1434,24 @@
       </c>
       <c r="C36" s="26" t="inlineStr">
         <is>
-          <t>User Chuyên viên nhập liệu</t>
+          <t>User Chi nhánh</t>
         </is>
       </c>
       <c r="D36" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước DetailDataEntry, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước BranchSupport, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E36" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DetailDataEntry' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'BranchSupport' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="28" t="inlineStr">
         <is>
-          <t>QC_USER</t>
+          <t>DDE_USER</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
@@ -1461,24 +1461,24 @@
       </c>
       <c r="C37" s="26" t="inlineStr">
         <is>
-          <t>User Kiểm soát nhập liệu</t>
+          <t>User Chuyên viên nhập liệu</t>
         </is>
       </c>
       <c r="D37" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước DataInputerChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước DetailDataEntry, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E37" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DataInputerChecker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DetailDataEntry' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="60" customHeight="1">
       <c r="A38" s="28" t="inlineStr">
         <is>
-          <t>UND_MAKER_USER</t>
+          <t>QC_USER</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
@@ -1488,24 +1488,24 @@
       </c>
       <c r="C38" s="26" t="inlineStr">
         <is>
-          <t>User Chuyên viên thẩm định</t>
+          <t>User Kiểm soát nhập liệu</t>
         </is>
       </c>
       <c r="D38" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước UnderwriterMaker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước DataInputerChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E38" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterMaker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DataInputerChecker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="39" ht="60" customHeight="1">
       <c r="A39" s="28" t="inlineStr">
         <is>
-          <t>UND_CHECKER_USER</t>
+          <t>UND_MAKER_USER</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
@@ -1515,24 +1515,24 @@
       </c>
       <c r="C39" s="26" t="inlineStr">
         <is>
-          <t>User Kiểm soát thẩm định</t>
+          <t>User Chuyên viên thẩm định</t>
         </is>
       </c>
       <c r="D39" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước UnderwriterChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước UnderwriterMaker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E39" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterChecker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterMaker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="60" customHeight="1">
       <c r="A40" s="28" t="inlineStr">
         <is>
-          <t>PHV_USER</t>
+          <t>UND_CHECKER_USER</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
@@ -1542,78 +1542,78 @@
       </c>
       <c r="C40" s="26" t="inlineStr">
         <is>
-          <t>User Chuyên viên Thẩm định điện thoại</t>
+          <t>User Kiểm soát thẩm định</t>
         </is>
       </c>
       <c r="D40" s="54" t="inlineStr">
         <is>
-          <t>User xử lý bước PhoneVerification, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>User xử lý bước UnderwriterChecker, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E40" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'PhoneVerification' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterChecker' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="41" ht="60" customHeight="1">
       <c r="A41" s="28" t="inlineStr">
         <is>
+          <t>PHV_USER</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="inlineStr">
+        <is>
+          <t>User Chuyên viên Thẩm định điện thoại</t>
+        </is>
+      </c>
+      <c r="D41" s="54" t="inlineStr">
+        <is>
+          <t>User xử lý bước PhoneVerification, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'PhoneVerification' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
           <t>APPROVER_USER</t>
         </is>
       </c>
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B42" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C41" s="26" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>User Chuyên gia phê duyệt</t>
         </is>
       </c>
-      <c r="D41" s="54" t="inlineStr">
+      <c r="D42" s="54" t="inlineStr">
         <is>
           <t>User xử lý bước CreditApproval, HOÀN TẤT gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E41" s="31" t="inlineStr">
+      <c r="E42" s="31" t="inlineStr">
         <is>
           <t>(SELECT WE.USERNAME FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'CreditApproval' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
-        <is>
-          <t>PROCESSED_DATE</t>
-        </is>
-      </c>
-      <c r="B42" s="25" t="inlineStr">
-        <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C42" s="26" t="inlineStr">
-        <is>
-          <t>Ngày xử lý hồ sơ</t>
-        </is>
-      </c>
-      <c r="D42" s="54" t="inlineStr">
-        <is>
-          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.PROCESSED_DATE</t>
-        </is>
-      </c>
-      <c r="E42" s="31" t="inlineStr">
-        <is>
-          <t>A.PROCESSED_DATE</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="28" t="inlineStr">
         <is>
-          <t>CREATION_DATE</t>
+          <t>PROCESSED_DATE</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
@@ -1623,24 +1623,24 @@
       </c>
       <c r="C43" s="26" t="inlineStr">
         <is>
-          <t>Ngày khởi tạo hồ sơ</t>
+          <t>Ngày xử lý hồ sơ</t>
         </is>
       </c>
       <c r="D43" s="54" t="inlineStr">
         <is>
-          <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CREATION_DATE</t>
+          <t>Ngày xử lý chung của hồ sơ theo 3 mức ưu tiên — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.PROCESSED_DATE</t>
         </is>
       </c>
       <c r="E43" s="31" t="inlineStr">
         <is>
-          <t>A.CREATION_DATE</t>
+          <t>A.PROCESSED_DATE</t>
         </is>
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="28" t="inlineStr">
         <is>
-          <t>LAST_APPROVAL_DATE</t>
+          <t>CREATION_DATE</t>
         </is>
       </c>
       <c r="B44" s="25" t="inlineStr">
@@ -1650,240 +1650,240 @@
       </c>
       <c r="C44" s="26" t="inlineStr">
         <is>
-          <t>Thời gian phê duyệt cuối</t>
+          <t>Ngày khởi tạo hồ sơ</t>
         </is>
       </c>
       <c r="D44" s="54" t="inlineStr">
         <is>
-          <t>MAX(EXITDATE) tại bước phê duyệt (nhóm quyết định đã định nghĩa) — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>TRUNC(MIN(ENTRYDATE)) theo WI_NAME — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CREATION_DATE</t>
         </is>
       </c>
       <c r="E44" s="31" t="inlineStr">
         <is>
-          <t>N1.LAST_APPROVAL_DATE</t>
+          <t>A.CREATION_DATE</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="28" t="inlineStr">
         <is>
-          <t>MIN_UWM</t>
+          <t>LAST_APPROVAL_DATE</t>
         </is>
       </c>
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>TIMESTAMP</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C45" s="26" t="inlineStr">
         <is>
-          <t>Thời gian hồ sơ lên CV thẩm định</t>
+          <t>Thời gian phê duyệt cuối</t>
         </is>
       </c>
       <c r="D45" s="54" t="inlineStr">
         <is>
-          <t>MIN(ENTRYDATE) tại UnderwriterMaker — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>MAX(EXITDATE) tại bước phê duyệt (nhóm quyết định đã định nghĩa) — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E45" s="31" t="inlineStr">
         <is>
-          <t>N2.MIN_UWM</t>
+          <t>N1.LAST_APPROVAL_DATE</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="28" t="inlineStr">
         <is>
+          <t>MIN_UWM</t>
+        </is>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian hồ sơ lên CV thẩm định</t>
+        </is>
+      </c>
+      <c r="D46" s="54" t="inlineStr">
+        <is>
+          <t>MIN(ENTRYDATE) tại UnderwriterMaker — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>N2.MIN_UWM</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
           <t>MIN_APP</t>
         </is>
       </c>
-      <c r="B46" s="25" t="inlineStr">
+      <c r="B47" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C46" s="26" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>Thời gian hồ sơ lên CG phê duyệt</t>
         </is>
       </c>
-      <c r="D46" s="54" t="inlineStr">
+      <c r="D47" s="54" t="inlineStr">
         <is>
           <t>MIN(ENTRYDATE) tại CreditApproval/CreditCommittee — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E46" s="31" t="inlineStr">
+      <c r="E47" s="31" t="inlineStr">
         <is>
           <t>N3.MIN_APP</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="60" customHeight="1">
-      <c r="A47" s="28" t="inlineStr">
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="28" t="inlineStr">
         <is>
           <t>CANCEL_USER_DATE</t>
         </is>
       </c>
-      <c r="B47" s="25" t="inlineStr">
+      <c r="B48" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C47" s="26" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>Thời gian cancel do NSD</t>
         </is>
       </c>
-      <c r="D47" s="54" t="inlineStr">
+      <c r="D48" s="54" t="inlineStr">
         <is>
           <t>EXITDATE tại bản ghi DECISION='Cancel' và USERNAME khác NULL — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E47" s="31" t="inlineStr">
+      <c r="E48" s="31" t="inlineStr">
         <is>
           <t>(SELECT WE.EXITDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE LEFT JOIN F WD ON WD.DIMENSION_KEY = WE.WORKSTEP_DECISION_SK WHERE WE.WI_NAME = A.WI_NAME AND WD.DECISION_CODE = 'Cancel' AND WE.USERNAME IS NOT NULL)</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="45" customHeight="1">
-      <c r="A48" s="28" t="inlineStr">
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="28" t="inlineStr">
         <is>
           <t>CANCEL_DATE</t>
         </is>
       </c>
-      <c r="B48" s="25" t="inlineStr">
+      <c r="B49" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C48" s="26" t="inlineStr">
+      <c r="C49" s="26" t="inlineStr">
         <is>
           <t>Thời gian vào vùng CancelRevoke</t>
         </is>
       </c>
-      <c r="D48" s="54" t="inlineStr">
+      <c r="D49" s="54" t="inlineStr">
         <is>
           <t>ENTRYDATE tại bước CancelRevoke — PHÁI SINH TẠI PDTD_DTM. FLAG_AUTO_CANCEL (business rule dựa trên cột này) tiếp tục tính tại chính bảng này, nay dùng input từ cột đã derive cùng bảng</t>
         </is>
       </c>
-      <c r="E48" s="31" t="inlineStr">
+      <c r="E49" s="31" t="inlineStr">
         <is>
           <t>N4.ENTRYDATE</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>LAST_ENTRYDATE</t>
-        </is>
-      </c>
-      <c r="B49" s="25" t="inlineStr">
-        <is>
-          <t>TIMESTAMP</t>
-        </is>
-      </c>
-      <c r="C49" s="26" t="inlineStr">
-        <is>
-          <t>Thời gian vào bước cuối</t>
-        </is>
-      </c>
-      <c r="D49" s="54" t="inlineStr">
-        <is>
-          <t>ENTRYDATE của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E49" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT WE.ENTRYDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="60" customHeight="1">
       <c r="A50" s="28" t="inlineStr">
         <is>
+          <t>LAST_ENTRYDATE</t>
+        </is>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Thời gian vào bước cuối</t>
+        </is>
+      </c>
+      <c r="D50" s="54" t="inlineStr">
+        <is>
+          <t>ENTRYDATE của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.ENTRYDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
           <t>LAST_EXITDATE</t>
         </is>
       </c>
-      <c r="B50" s="25" t="inlineStr">
+      <c r="B51" s="25" t="inlineStr">
         <is>
           <t>TIMESTAMP</t>
         </is>
       </c>
-      <c r="C50" s="26" t="inlineStr">
+      <c r="C51" s="26" t="inlineStr">
         <is>
           <t>Thời gian kết thúc bước cuối</t>
         </is>
       </c>
-      <c r="D50" s="54" t="inlineStr">
+      <c r="D51" s="54" t="inlineStr">
         <is>
           <t>EXITDATE của cùng sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E50" s="31" t="inlineStr">
+      <c r="E51" s="31" t="inlineStr">
         <is>
           <t>(SELECT WE.EXITDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
         <is>
           <t>PRE_WORKSTEP_CODE</t>
         </is>
       </c>
-      <c r="B51" s="25" t="inlineStr">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C51" s="26" t="inlineStr">
+      <c r="C52" s="26" t="inlineStr">
         <is>
           <t>Bước hồ sơ trước đó</t>
         </is>
       </c>
-      <c r="D51" s="54" t="inlineStr">
+      <c r="D52" s="54" t="inlineStr">
         <is>
           <t>Bước xử lý liền trước (LAG theo ENTRYDATE) — PHÁI SINH TẠI PDTD_DTM, của sự kiện hoàn tất gần nhất</t>
         </is>
       </c>
-      <c r="E51" s="31" t="inlineStr">
+      <c r="E52" s="31" t="inlineStr">
         <is>
           <t>LAG(E.WORKSTEP_CODE) OVER (PARTITION BY E.WI_NAME ORDER BY E.ENTRYDATE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>LAST_REMARKS</t>
-        </is>
-      </c>
-      <c r="B52" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(4000)</t>
-        </is>
-      </c>
-      <c r="C52" s="26" t="inlineStr">
-        <is>
-          <t>Ghi chú ý kiến bước cuối</t>
-        </is>
-      </c>
-      <c r="D52" s="54" t="inlineStr">
-        <is>
-          <t>Ghi chú của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
-        </is>
-      </c>
-      <c r="E52" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="60" customHeight="1">
       <c r="A53" s="28" t="inlineStr">
         <is>
-          <t>LAST_REMARK_DDE</t>
+          <t>LAST_REMARKS</t>
         </is>
       </c>
       <c r="B53" s="25" t="inlineStr">
@@ -1893,159 +1893,159 @@
       </c>
       <c r="C53" s="26" t="inlineStr">
         <is>
-          <t>Ghi chú tại bước DDE</t>
+          <t>Ghi chú ý kiến bước cuối</t>
         </is>
       </c>
       <c r="D53" s="54" t="inlineStr">
         <is>
-          <t>Ghi chú tại bước DetailDataEntry — PHÁI SINH TẠI PDTD_DTM</t>
+          <t>Ghi chú của sự kiện hoàn tất gần nhất — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
       <c r="E53" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DetailDataEntry' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.EXITDATE IS NOT NULL AND WE.ENTRYDATE &lt;= v_batch_date ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="60" customHeight="1">
       <c r="A54" s="28" t="inlineStr">
         <is>
+          <t>LAST_REMARK_DDE</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(4000)</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="inlineStr">
+        <is>
+          <t>Ghi chú tại bước DDE</t>
+        </is>
+      </c>
+      <c r="D54" s="54" t="inlineStr">
+        <is>
+          <t>Ghi chú tại bước DetailDataEntry — PHÁI SINH TẠI PDTD_DTM</t>
+        </is>
+      </c>
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'DetailDataEntry' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
           <t>LAST_CAN_REMARKS</t>
         </is>
       </c>
-      <c r="B54" s="25" t="inlineStr">
+      <c r="B55" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(4000)</t>
         </is>
       </c>
-      <c r="C54" s="26" t="inlineStr">
+      <c r="C55" s="26" t="inlineStr">
         <is>
           <t>Ghi chú tại bước Cancel</t>
         </is>
       </c>
-      <c r="D54" s="54" t="inlineStr">
+      <c r="D55" s="54" t="inlineStr">
         <is>
           <t>Ghi chú tại lần hủy hồ sơ — PHÁI SINH TẠI PDTD_DTM</t>
         </is>
       </c>
-      <c r="E54" s="31" t="inlineStr">
+      <c r="E55" s="31" t="inlineStr">
         <is>
           <t>(SELECT WE.REMARKS FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'CancelRevoke' AND WE.EXITDATE &lt;= v_batch_date ORDER BY WE.EXITDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-      <c r="B55" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(25,2)</t>
-        </is>
-      </c>
-      <c r="C55" s="26" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối</t>
-        </is>
-      </c>
-      <c r="D55" s="54" t="inlineStr">
-        <is>
-          <t>Hạn mức phê duyệt cuối cùng — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_AMT_FINAL</t>
-        </is>
-      </c>
-      <c r="E55" s="31" t="inlineStr">
-        <is>
-          <t>A.APPROVED_AMT_FINAL</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="28" t="inlineStr">
         <is>
-          <t>APPROVED_TERM</t>
+          <t>APPROVED_AMT_FINAL</t>
         </is>
       </c>
       <c r="B56" s="25" t="inlineStr">
         <is>
-          <t>NUMBER(15)</t>
+          <t>NUMBER(25,2)</t>
         </is>
       </c>
       <c r="C56" s="26" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt</t>
+          <t>Hạn mức phê duyệt cuối</t>
         </is>
       </c>
       <c r="D56" s="54" t="inlineStr">
         <is>
-          <t>Kỳ hạn phê duyệt — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_TERM</t>
+          <t>Hạn mức phê duyệt cuối cùng — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_AMT_FINAL</t>
         </is>
       </c>
       <c r="E56" s="31" t="inlineStr">
         <is>
-          <t>A.APPROVED_TERM</t>
+          <t>A.APPROVED_AMT_FINAL</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="28" t="inlineStr">
         <is>
+          <t>APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(15)</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt</t>
+        </is>
+      </c>
+      <c r="D57" s="54" t="inlineStr">
+        <is>
+          <t>Kỳ hạn phê duyệt — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.APPROVED_TERM</t>
+        </is>
+      </c>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>A.APPROVED_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
           <t>CURRENCY_CODE</t>
         </is>
       </c>
-      <c r="B57" s="25" t="inlineStr">
+      <c r="B58" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C57" s="26" t="inlineStr">
+      <c r="C58" s="26" t="inlineStr">
         <is>
           <t>Loại tiền</t>
         </is>
       </c>
-      <c r="D57" s="54" t="inlineStr">
+      <c r="D58" s="54" t="inlineStr">
         <is>
           <t>Loại tiền (BC3.CURRENCY) — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CURRENCY_CODE</t>
         </is>
       </c>
-      <c r="E57" s="31" t="inlineStr">
+      <c r="E58" s="31" t="inlineStr">
         <is>
           <t>A.CURRENCY_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="60" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>UNDERWRITERMAKER_USERMAKE</t>
-        </is>
-      </c>
-      <c r="B58" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(100)</t>
-        </is>
-      </c>
-      <c r="C58" s="26" t="inlineStr">
-        <is>
-          <t>User Maker CVTĐ</t>
-        </is>
-      </c>
-      <c r="D58" s="54" t="inlineStr">
-        <is>
-          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
-        </is>
-      </c>
-      <c r="E58" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT WE.UNDERWRITERMAKER_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterMaker' ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="28" t="inlineStr">
         <is>
-          <t>UNDERWRITERCHECKER_USERMAKE</t>
+          <t>UNDERWRITERMAKER_USERMAKE</t>
         </is>
       </c>
       <c r="B59" s="25" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C59" s="26" t="inlineStr">
         <is>
-          <t>User Checker CVTĐ</t>
+          <t>User Maker CVTĐ</t>
         </is>
       </c>
       <c r="D59" s="54" t="inlineStr">
@@ -2065,311 +2065,311 @@
       </c>
       <c r="E59" s="31" t="inlineStr">
         <is>
-          <t>(SELECT WE.UNDERWRITERCHECKER_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterChecker' ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+          <t>(SELECT WE.UNDERWRITERMAKER_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterMaker' ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
         </is>
       </c>
     </row>
     <row r="60" ht="60" customHeight="1">
       <c r="A60" s="28" t="inlineStr">
         <is>
+          <t>UNDERWRITERCHECKER_USERMAKE</t>
+        </is>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="inlineStr">
+        <is>
+          <t>User Checker CVTĐ</t>
+        </is>
+      </c>
+      <c r="D60" s="54" t="inlineStr">
+        <is>
+          <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
+        </is>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT WE.UNDERWRITERCHECKER_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE = 'UnderwriterChecker' ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
           <t>APPROVAL_USERMAKE</t>
         </is>
       </c>
-      <c r="B60" s="25" t="inlineStr">
+      <c r="B61" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C60" s="26" t="inlineStr">
+      <c r="C61" s="26" t="inlineStr">
         <is>
           <t>User Maker phê duyệt</t>
         </is>
       </c>
-      <c r="D60" s="54" t="inlineStr">
+      <c r="D61" s="54" t="inlineStr">
         <is>
           <t>PHÁI SINH, COALESCE ĐÃ TÍNH XONG TẠI SB_DWH</t>
         </is>
       </c>
-      <c r="E60" s="31" t="inlineStr">
+      <c r="E61" s="31" t="inlineStr">
         <is>
           <t>(SELECT WE.APPROVAL_USERMAKE FROM STG_FCT_RLOS_WORKSTEP_EVENT WE WHERE WE.WI_NAME = A.WI_NAME AND WE.WORKSTEP_CODE IN ('CreditCommittee','CreditApproval') ORDER BY WE.ENTRYDATE DESC FETCH FIRST 1 ROW ONLY)</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>CHANGE_REQUEST</t>
-        </is>
-      </c>
-      <c r="B61" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(200)</t>
-        </is>
-      </c>
-      <c r="C61" s="26" t="inlineStr">
-        <is>
-          <t>Yêu cầu điều chỉnh hồ sơ</t>
-        </is>
-      </c>
-      <c r="D61" s="54" t="inlineStr">
-        <is>
-          <t>Yêu cầu điều chỉnh hồ sơ — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_REQUEST</t>
-        </is>
-      </c>
-      <c r="E61" s="31" t="inlineStr">
-        <is>
-          <t>A.CHANGE_REQUEST</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="28" t="inlineStr">
         <is>
+          <t>CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ</t>
+        </is>
+      </c>
+      <c r="D62" s="54" t="inlineStr">
+        <is>
+          <t>Yêu cầu điều chỉnh hồ sơ — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_REQUEST</t>
+        </is>
+      </c>
+      <c r="E62" s="31" t="inlineStr">
+        <is>
+          <t>A.CHANGE_REQUEST</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
           <t>CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="B62" s="25" t="inlineStr">
+      <c r="B63" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(500)</t>
         </is>
       </c>
-      <c r="C62" s="26" t="inlineStr">
+      <c r="C63" s="26" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện</t>
         </is>
       </c>
-      <c r="D62" s="54" t="inlineStr">
+      <c r="D63" s="54" t="inlineStr">
         <is>
           <t>Loại thay đổi điều kiện phê duyệt — bê 1:1 từ SB_DWH.FCT_RLOS_APPLICATION.CHANGE_TYPE</t>
         </is>
       </c>
-      <c r="E62" s="31" t="inlineStr">
+      <c r="E63" s="31" t="inlineStr">
         <is>
           <t>A.CHANGE_TYPE</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="60" customHeight="1">
-      <c r="A63" s="28" t="inlineStr">
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_STATUS</t>
         </is>
       </c>
-      <c r="B63" s="25" t="inlineStr">
+      <c r="B64" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C63" s="26" t="inlineStr">
+      <c r="C64" s="26" t="inlineStr">
         <is>
           <t>Trạng thái hồ sơ</t>
         </is>
       </c>
-      <c r="D63" s="54" t="inlineStr">
+      <c r="D64" s="54" t="inlineStr">
         <is>
           <t>Trạng thái hồ sơ chuẩn hóa (BC1) — PHÁI SINH TẠI PDTD_DTM, business rule (đồng bộ theo pattern CLOS)</t>
         </is>
       </c>
-      <c r="E63" s="31" t="inlineStr">
+      <c r="E64" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN F.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport') THEN 'Approved' WHEN F.DECISION_CODE = 'Reject' THEN 'Rejected' WHEN F.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent') THEN 'Cancelled' ELSE 'Processing' END</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="180" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
+    <row r="65" ht="180" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>AUTO_CANCEL_DATE</t>
         </is>
       </c>
-      <c r="B64" s="25" t="inlineStr">
+      <c r="B65" s="25" t="inlineStr">
         <is>
           <t>DATE</t>
         </is>
       </c>
-      <c r="C64" s="26" t="inlineStr">
+      <c r="C65" s="26" t="inlineStr">
         <is>
           <t>Thời gian cancel tự động</t>
         </is>
       </c>
-      <c r="D64" s="54" t="inlineStr">
-        <is>
-          <t>Ngày hồ sơ bị hệ thống tự động chuyển sang CancelRevoke (BC1.AUTO_CAN_DATE) — PHÁI SINH TẠI PDTD_DTM. MIN(ENTRYDATE) tại CancelRevoke thỏa 1 trong 2 nhánh — (1) dòng đang mở hoàn toàn, (2) từng treo tại BranchSupport ≥2400 phút nghiệp vụ (GET_BUSINESS_MINUTE) trước khi vào CancelRevoke — loại trừ hồ sơ có bước hủy thủ công (DECISION_CODE='Cancel') trước/cùng thời điểm.</t>
-        </is>
-      </c>
-      <c r="E64" s="31" t="inlineStr">
-        <is>
-          <t>(SELECT MIN(E.ENTRYDATE) FROM STG_FCT_RLOS_WORKSTEP_EVENT E LEFT JOIN F WD ON WD.DIMENSION_KEY = E.WORKSTEP_DECISION_SK WHERE E.WI_NAME = A.WI_NAME AND E.WORKSTEP_CODE = 'CancelRevoke' AND ( (E.USERNAME IS NULL AND E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL) OR (E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT BS WHERE BS.WI_NAME = E.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT C LEFT JOIN STG_DIM_RLOS_WORKSTEP_DECISION WDC ON WDC.DIMENSION_KEY = C.WORKSTEP_DECISION_SK WHERE C.WI_NAME = E.WI_NAME AND WDC.DECISION_CODE = 'Cancel' AND C.ENTRYDATE &lt;= E.ENTRYDATE))</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="195" customHeight="1">
-      <c r="A65" s="28" t="inlineStr">
+      <c r="D65" s="54" t="inlineStr">
+        <is>
+          <t>Ngày hồ sơ bị hệ thống tự động chuyển sang CancelRevoke (BC1.AUTO_CAN_DATE) — PHÁI SINH TẠI PDTD_DTM. MIN(ENTRYDATE) tại CancelRevoke thỏa điều kiện Auto-Cancel (dòng đang mở hoàn toàn, hoặc treo tại BranchSupport ≥2400 phút nghiệp vụ), loại trừ hồ sơ có bước hủy thủ công trước/cùng thời điểm.</t>
+        </is>
+      </c>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>(SELECT MIN(E.ENTRYDATE) FROM STG_FCT_RLOS_WORKSTEP_EVENT E LEFT JOIN F WD ON WD.DIMENSION_KEY = E.WORKSTEP_DECISION_SK WHERE E.WI_NAME = A.WI_NAME AND E.WORKSTEP_CODE = 'CancelRevoke' AND ( (E.USERNAME IS NULL AND E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL) OR (E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT BS WHERE BS.WI_NAME = E.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT C LEFT JOIN F WDC ON WDC.DIMENSION_KEY = C.WORKSTEP_DECISION_SK WHERE C.WI_NAME = E.WI_NAME AND WDC.DECISION_CODE = 'Cancel' AND C.ENTRYDATE &lt;= E.ENTRYDATE))</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="180" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
         <is>
           <t>FLAG_AUTO_CANCEL</t>
         </is>
       </c>
-      <c r="B65" s="25" t="inlineStr">
+      <c r="B66" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C65" s="26" t="inlineStr">
+      <c r="C66" s="26" t="inlineStr">
         <is>
           <t>Hồ sơ cancel tự động</t>
         </is>
       </c>
-      <c r="D65" s="54" t="inlineStr">
+      <c r="D66" s="54" t="inlineStr">
         <is>
           <t>'YES'/'NO' theo nguyên văn SRS BC1 field FLAG_AUTO_CAN (BC1) — PHÁI SINH TẠI PDTD_DTM. YES nếu tồn tại dòng CancelRevoke thỏa cùng điều kiện Auto-Cancel đã mô tả ở AUTO_CANCEL_DATE.</t>
         </is>
       </c>
-      <c r="E65" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT E LEFT JOIN F WD ON WD.DIMENSION_KEY = E.WORKSTEP_DECISION_SK WHERE E.WI_NAME = A.WI_NAME AND E.WORKSTEP_CODE = 'CancelRevoke' AND ( (E.USERNAME IS NULL AND E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL) OR (E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT BS WHERE BS.WI_NAME = E.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT C LEFT JOIN STG_DIM_RLOS_WORKSTEP_DECISION WDC ON WDC.DIMENSION_KEY = C.WORKSTEP_DECISION_SK WHERE C.WI_NAME = E.WI_NAME AND WDC.DECISION_CODE = 'Cancel' AND C.ENTRYDATE &lt;= E.ENTRYDATE)) THEN 'YES' ELSE 'NO' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT E LEFT JOIN F WD ON WD.DIMENSION_KEY = E.WORKSTEP_DECISION_SK WHERE E.WI_NAME = A.WI_NAME AND E.WORKSTEP_CODE = 'CancelRevoke' AND ( (E.USERNAME IS NULL AND E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL) OR (E.EXITDATE IS NULL AND WD.DECISION_CODE IS NULL AND EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT BS WHERE BS.WI_NAME = E.WI_NAME AND BS.WORKSTEP_CODE = 'BranchSupport' AND BS.ENTRYDATE &lt; E.ENTRYDATE AND GET_BUSINESS_MINUTE(BS.ENTRYDATE, E.ENTRYDATE) &gt;= 2400)) ) AND NOT EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT C LEFT JOIN F WDC ON WDC.DIMENSION_KEY = C.WORKSTEP_DECISION_SK WHERE C.WI_NAME = E.WI_NAME AND WDC.DECISION_CODE = 'Cancel' AND C.ENTRYDATE &lt;= E.ENTRYDATE)) THEN 'YES' ELSE 'NO' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="90" customHeight="1">
+      <c r="A67" s="28" t="inlineStr">
         <is>
           <t>LAST_WORKSTEP</t>
         </is>
       </c>
-      <c r="B66" s="25" t="inlineStr">
+      <c r="B67" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C66" s="26" t="inlineStr">
+      <c r="C67" s="26" t="inlineStr">
         <is>
           <t>Bước hồ sơ cuối cùng</t>
         </is>
       </c>
-      <c r="D66" s="54" t="inlineStr">
-        <is>
-          <t>Tên bước hoàn tất gần nhất, chuẩn hóa dùng chung 2 hệ. [CẦN REVIEW] etl_logic gốc chỉ viết '...' không spell rõ điều kiện JOIN đầy đủ (note nhắc hop qua WORKSTEP_DECISION_SK, cùng pattern CLOS) — cần xác nhận lại chuỗi JOIN đầy đủ.</t>
-        </is>
-      </c>
-      <c r="E66" s="31" t="inlineStr">
+      <c r="D67" s="54" t="inlineStr">
+        <is>
+          <t>Tên bước hoàn tất gần nhất, chuẩn hóa dùng chung 2 hệ. [CẦN REVIEW] etl_logic gốc không spell rõ điều kiện JOIN đầy đủ sang Q_RLOS_REF_WORKSTEP_2SYSTEMS theo WORKSTEP_CODE/DECISION_CODE tra qua WORKSTEP_DECISION_SK — giữ nguyên theo đúng LLD, cần xác nhận lại JOIN chain khi review.</t>
+        </is>
+      </c>
+      <c r="E67" s="31" t="inlineStr">
         <is>
           <t>G.WORKSTEP_NAME_STD</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="28" t="inlineStr">
         <is>
           <t>BUSINESS_FLOW</t>
         </is>
       </c>
-      <c r="B67" s="25" t="inlineStr">
+      <c r="B68" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(50)</t>
         </is>
       </c>
-      <c r="C67" s="26" t="inlineStr">
+      <c r="C68" s="26" t="inlineStr">
         <is>
           <t>Phân khúc hồ sơ</t>
         </is>
       </c>
-      <c r="D67" s="54" t="inlineStr">
+      <c r="D68" s="54" t="inlineStr">
         <is>
           <t>Luồng nghiệp vụ chuẩn hóa để hiển thị trên báo cáo</t>
         </is>
       </c>
-      <c r="E67" s="31" t="inlineStr">
+      <c r="E68" s="31" t="inlineStr">
         <is>
           <t>H.BUSINESS_FLOW</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="28" t="inlineStr">
+    <row r="69" ht="60" customHeight="1">
+      <c r="A69" s="28" t="inlineStr">
         <is>
           <t>DEVIATION_G3</t>
         </is>
       </c>
-      <c r="B68" s="25" t="inlineStr">
+      <c r="B69" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(10)</t>
         </is>
       </c>
-      <c r="C68" s="26" t="inlineStr">
+      <c r="C69" s="26" t="inlineStr">
         <is>
           <t>Hồ sơ có từ 3 ngoại lệ</t>
         </is>
       </c>
-      <c r="D68" s="54" t="inlineStr">
+      <c r="D69" s="54" t="inlineStr">
         <is>
           <t>Hồ sơ có từ 3 ngoại lệ chính sách trở lên hay không (YES/NO) — CHUYỂN TỪ DIM_RLOS_APPLICATION</t>
         </is>
       </c>
-      <c r="E68" s="31" t="inlineStr">
+      <c r="E69" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN (SELECT COUNT(*) FROM STG_FCT_RLOS_DEVIATION DV WHERE DV.WI_NAME = A.WI_NAME AND DV.DAYID = (SELECT MAX(DAYID) FROM STG_FCT_RLOS_DEVIATION WHERE WI_NAME = A.WI_NAME)) &gt;= 3 THEN 'YES' ELSE 'NO' END</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="45" customHeight="1">
-      <c r="A69" s="28" t="inlineStr">
+    <row r="70" ht="75" customHeight="1">
+      <c r="A70" s="28" t="inlineStr">
         <is>
           <t>REF_PRODUCT</t>
         </is>
       </c>
-      <c r="B69" s="25" t="inlineStr">
+      <c r="B70" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C69" s="26" t="inlineStr">
+      <c r="C70" s="26" t="inlineStr">
         <is>
           <t>Nhóm sản phẩm tra SLA</t>
         </is>
       </c>
-      <c r="D69" s="54" t="inlineStr">
-        <is>
-          <t>Nhóm sản phẩm dùng để tra cam kết SLA (BC5) — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM. either/or theo PRODUCTLINE_NAME hoặc CHANGE_TYPE.</t>
-        </is>
-      </c>
-      <c r="E69" s="31" t="inlineStr">
+      <c r="D70" s="54" t="inlineStr">
+        <is>
+          <t>Nhóm sản phẩm dùng để tra cam kết SLA (BC5) — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM. either/or theo PRODUCTLINE_NAME hoặc CHANGE_TYPE (chỉ so khớp CHANGE_TYPE khi dòng REF_ có PRODUCT_LINE='Trường Change Request').</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
         <is>
           <t>K.REF_PRODUCT</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>SLA_CREDIT_OFFICER</t>
-        </is>
-      </c>
-      <c r="B70" s="25" t="inlineStr">
-        <is>
-          <t>NUMBER(10,2)</t>
-        </is>
-      </c>
-      <c r="C70" s="26" t="inlineStr">
-        <is>
-          <t>Cam kết SLA chuyên viên tín dụng</t>
-        </is>
-      </c>
-      <c r="D70" s="54" t="inlineStr">
-        <is>
-          <t>Cam kết giờ cho chuyên viên tín dụng — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
-        </is>
-      </c>
-      <c r="E70" s="31" t="inlineStr">
-        <is>
-          <t>K.SLA_CREDIT_OFFICER</t>
         </is>
       </c>
     </row>
     <row r="71" ht="45" customHeight="1">
       <c r="A71" s="28" t="inlineStr">
         <is>
-          <t>SLA_MARKER</t>
+          <t>SLA_CREDIT_OFFICER</t>
         </is>
       </c>
       <c r="B71" s="25" t="inlineStr">
@@ -2379,24 +2379,24 @@
       </c>
       <c r="C71" s="26" t="inlineStr">
         <is>
-          <t>Cam kết SLA lập hồ sơ thẩm định</t>
+          <t>Cam kết SLA chuyên viên tín dụng</t>
         </is>
       </c>
       <c r="D71" s="54" t="inlineStr">
         <is>
-          <t>Cam kết giờ cho bước lập hồ sơ thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+          <t>Cam kết giờ cho chuyên viên tín dụng — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
         </is>
       </c>
       <c r="E71" s="31" t="inlineStr">
         <is>
-          <t>K.SLA_MARKER</t>
+          <t>K.SLA_CREDIT_OFFICER</t>
         </is>
       </c>
     </row>
     <row r="72" ht="45" customHeight="1">
       <c r="A72" s="28" t="inlineStr">
         <is>
-          <t>SLA_CHECKER</t>
+          <t>SLA_MARKER</t>
         </is>
       </c>
       <c r="B72" s="25" t="inlineStr">
@@ -2406,230 +2406,246 @@
       </c>
       <c r="C72" s="26" t="inlineStr">
         <is>
-          <t>Cam kết SLA kiểm soát thẩm định</t>
+          <t>Cam kết SLA lập hồ sơ thẩm định</t>
         </is>
       </c>
       <c r="D72" s="54" t="inlineStr">
         <is>
-          <t>Cam kết giờ cho bước kiểm soát thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+          <t>Cam kết giờ cho bước lập hồ sơ thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
         </is>
       </c>
       <c r="E72" s="31" t="inlineStr">
         <is>
-          <t>K.SLA_CHECKER</t>
+          <t>K.SLA_MARKER</t>
         </is>
       </c>
     </row>
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="28" t="inlineStr">
         <is>
+          <t>SLA_CHECKER</t>
+        </is>
+      </c>
+      <c r="B73" s="25" t="inlineStr">
+        <is>
+          <t>NUMBER(10,2)</t>
+        </is>
+      </c>
+      <c r="C73" s="26" t="inlineStr">
+        <is>
+          <t>Cam kết SLA kiểm soát thẩm định</t>
+        </is>
+      </c>
+      <c r="D73" s="54" t="inlineStr">
+        <is>
+          <t>Cam kết giờ cho bước kiểm soát thẩm định — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>K.SLA_CHECKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="45" customHeight="1">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
           <t>SLA_CREDIT_APPROVER</t>
         </is>
       </c>
-      <c r="B73" s="25" t="inlineStr">
+      <c r="B74" s="25" t="inlineStr">
         <is>
           <t>NUMBER(10,2)</t>
         </is>
       </c>
-      <c r="C73" s="26" t="inlineStr">
+      <c r="C74" s="26" t="inlineStr">
         <is>
           <t>Cam kết SLA cấp phê duyệt</t>
         </is>
       </c>
-      <c r="D73" s="54" t="inlineStr">
+      <c r="D74" s="54" t="inlineStr">
         <is>
           <t>Cam kết giờ cho cấp phê duyệt — CHUYỂN TỪ DIM_RLOS_APPLICATION, PHÁI SINH TẠI PDTD_DTM, cùng LEFT JOIN REF_ trên REF_PRODUCT</t>
         </is>
       </c>
-      <c r="E73" s="31" t="inlineStr">
+      <c r="E74" s="31" t="inlineStr">
         <is>
           <t>K.SLA_CREDIT_APPROVER</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="75" customHeight="1">
-      <c r="A74" s="28" t="inlineStr">
+    <row r="75" ht="75" customHeight="1">
+      <c r="A75" s="28" t="inlineStr">
         <is>
           <t>HAS_DDE_FLAG</t>
         </is>
       </c>
-      <c r="B74" s="25" t="inlineStr">
+      <c r="B75" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C74" s="26" t="inlineStr">
+      <c r="C75" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới DetailDataEntry</t>
         </is>
       </c>
-      <c r="D74" s="54" t="inlineStr">
+      <c r="D75" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước DetailDataEntry', chỉ chuyển Y, không bao giờ quay lại N. Nguồn cho VOLUME (AGG_LOS_KPI_APPLICATION) thay cho EXISTS quét lịch sử WORKSTEP_EVENT. Cùng cơ chế đã áp dụng cho FCT_CLOS_APPLICATION.</t>
         </is>
       </c>
-      <c r="E74" s="31" t="inlineStr">
+      <c r="E75" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN COALESCE(L.HAS_DDE_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'DetailDataEntry') THEN 'Y' ELSE 'N' END</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="28" t="inlineStr">
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="28" t="inlineStr">
         <is>
           <t>HAS_UWM_FLAG</t>
         </is>
       </c>
-      <c r="B75" s="25" t="inlineStr">
+      <c r="B76" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C75" s="26" t="inlineStr">
+      <c r="C76" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới UnderwriterMaker</t>
         </is>
       </c>
-      <c r="D75" s="54" t="inlineStr">
+      <c r="D76" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterMaker'. Dùng cho carry-forward hồ sơ treo trên FCT_RLOS_WORKSTEP_EVENT (lọc phạm vi BC4) và nguồn cho VOLUME</t>
         </is>
       </c>
-      <c r="E75" s="31" t="inlineStr">
+      <c r="E76" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN COALESCE(L.HAS_UWM_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterMaker') THEN 'Y' ELSE 'N' END</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>HAS_UWC_FLAG</t>
-        </is>
-      </c>
-      <c r="B76" s="25" t="inlineStr">
-        <is>
-          <t>VARCHAR2(1)</t>
-        </is>
-      </c>
-      <c r="C76" s="26" t="inlineStr">
-        <is>
-          <t>Cờ đã tới UnderwriterChecker</t>
-        </is>
-      </c>
-      <c r="D76" s="54" t="inlineStr">
-        <is>
-          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterChecker'. Nguồn cho VOLUME (mức 0.6)</t>
-        </is>
-      </c>
-      <c r="E76" s="31" t="inlineStr">
-        <is>
-          <t>CASE WHEN COALESCE(L.HAS_UWC_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterChecker') THEN 'Y' ELSE 'N' END</t>
         </is>
       </c>
     </row>
     <row r="77" ht="45" customHeight="1">
       <c r="A77" s="28" t="inlineStr">
         <is>
+          <t>HAS_UWC_FLAG</t>
+        </is>
+      </c>
+      <c r="B77" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(1)</t>
+        </is>
+      </c>
+      <c r="C77" s="26" t="inlineStr">
+        <is>
+          <t>Cờ đã tới UnderwriterChecker</t>
+        </is>
+      </c>
+      <c r="D77" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước UnderwriterChecker'. Nguồn cho VOLUME (mức 0.6)</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>CASE WHEN COALESCE(L.HAS_UWC_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE = 'UnderwriterChecker') THEN 'Y' ELSE 'N' END</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="45" customHeight="1">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
           <t>HAS_APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B77" s="25" t="inlineStr">
+      <c r="B78" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C77" s="26" t="inlineStr">
+      <c r="C78" s="26" t="inlineStr">
         <is>
           <t>Cờ đã tới cấp phê duyệt</t>
         </is>
       </c>
-      <c r="D77" s="54" t="inlineStr">
+      <c r="D78" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã từng tới bước CreditApproval/CreditCommittee' (chưa cần đã có quyết định). Nguồn cho VOLUME (mức 0.8)</t>
         </is>
       </c>
-      <c r="E77" s="31" t="inlineStr">
+      <c r="E78" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN COALESCE(L.HAS_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee')) THEN 'Y' ELSE 'N' END</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="90" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
+    <row r="79" ht="90" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
         <is>
           <t>HAS_FINAL_APPROVAL_FLAG</t>
         </is>
       </c>
-      <c r="B78" s="25" t="inlineStr">
+      <c r="B79" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C78" s="26" t="inlineStr">
+      <c r="C79" s="26" t="inlineStr">
         <is>
           <t>Cờ đã có quyết định phê duyệt</t>
         </is>
       </c>
-      <c r="D78" s="54" t="inlineStr">
+      <c r="D79" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã có quyết định phê duyệt hoàn tất' (case 1 của PROCESSED_DATE). Nguồn cho VOLUME mức 1.0</t>
         </is>
       </c>
-      <c r="E78" s="31" t="inlineStr">
+      <c r="E79" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN COALESCE(L.HAS_FINAL_APPROVAL_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e JOIN F wd ON wd.DIMENSION_KEY = e.WORKSTEP_DECISION_SK WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') AND wd.DECISION_CODE IN ('Submit','Send To PostSanction','Submit To DisbursementMaker','Send To HOSupport','Reject')) THEN 'Y' ELSE 'N' END</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="28" t="inlineStr">
+    <row r="80" ht="60" customHeight="1">
+      <c r="A80" s="28" t="inlineStr">
         <is>
           <t>HAS_CANCELLED_FLAG</t>
         </is>
       </c>
-      <c r="B79" s="25" t="inlineStr">
+      <c r="B80" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C79" s="26" t="inlineStr">
+      <c r="C80" s="26" t="inlineStr">
         <is>
           <t>Cờ đã bị hủy</t>
         </is>
       </c>
-      <c r="D79" s="54" t="inlineStr">
+      <c r="D80" s="54" t="inlineStr">
         <is>
           <t>CỘT MỚI — Cờ một chiều 'hồ sơ đã rơi vào CancelRevoke/CancelPermanent'. VOLUME dùng cờ này để xác nhận hồ sơ đã KẾT THÚC do hủy, lấy điểm theo bước xa nhất đã đạt trước khi hủy thay vì NULL</t>
         </is>
       </c>
-      <c r="E79" s="31" t="inlineStr">
+      <c r="E80" s="31" t="inlineStr">
         <is>
           <t>CASE WHEN COALESCE(L.HAS_CANCELLED_FLAG, 'N') = 'Y' OR EXISTS (SELECT 1 FROM STG_FCT_RLOS_WORKSTEP_EVENT e WHERE e.WI_NAME = A.WI_NAME AND e.WORKSTEP_CODE IN ('CancelRevoke','CancelPermanent')) THEN 'Y' ELSE 'N' END</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="10" t="n"/>
-      <c r="B81" s="10" t="n"/>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="55" t="inlineStr">
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="10" t="n"/>
+      <c r="B82" s="10" t="n"/>
+      <c r="C82" s="10" t="n"/>
+      <c r="D82" s="55" t="inlineStr">
         <is>
           <t>Điều kiện join giữa các bảng</t>
         </is>
       </c>
-      <c r="E81" s="10" t="n"/>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="25" t="n"/>
-      <c r="B82" s="25" t="n"/>
-      <c r="C82" s="51" t="n"/>
-      <c r="D82" s="54" t="n"/>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C.DIMENSION_KEY = A.APPLICATION_SK</t>
-        </is>
-      </c>
+      <c r="E82" s="10" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="25" t="n"/>
@@ -2638,7 +2654,7 @@
       <c r="D83" s="54" t="n"/>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN B.MAIN_ID = C.RESULT_MAIN_CARD_ID</t>
+          <t>LEFT JOIN C.DIMENSION_KEY = A.APPLICATION_SK</t>
         </is>
       </c>
     </row>
@@ -2649,84 +2665,84 @@
       <c r="D84" s="54" t="n"/>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN D.RECID = C.RESULT_MAIN_CARD_ID</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="60" customHeight="1">
+          <t>LEFT JOIN B.MAIN_ID = C.RESULT_MAIN_CARD_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
       <c r="A85" s="25" t="n"/>
       <c r="B85" s="25" t="n"/>
       <c r="C85" s="51" t="n"/>
       <c r="D85" s="54" t="n"/>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN N1 (SELECT WI_NAME, MAX(EXITDATE) AS LAST_APPROVAL_DATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N1 ON N1.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="45" customHeight="1">
+          <t>LEFT JOIN D.RECID = C.RESULT_MAIN_CARD_ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="60" customHeight="1">
       <c r="A86" s="25" t="n"/>
       <c r="B86" s="25" t="n"/>
       <c r="C86" s="51" t="n"/>
       <c r="D86" s="54" t="n"/>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN N2 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_UWM FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'UnderwriterMaker' GROUP BY WI_NAME) N2 ON N2.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="60" customHeight="1">
+          <t>LEFT JOIN N1 (SELECT WI_NAME, MAX(EXITDATE) AS LAST_APPROVAL_DATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N1 ON N1.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="45" customHeight="1">
       <c r="A87" s="25" t="n"/>
       <c r="B87" s="25" t="n"/>
       <c r="C87" s="51" t="n"/>
       <c r="D87" s="54" t="n"/>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN N3 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_APP FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N3 ON N3.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="45" customHeight="1">
+          <t>LEFT JOIN N2 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_UWM FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'UnderwriterMaker' GROUP BY WI_NAME) N2 ON N2.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="60" customHeight="1">
       <c r="A88" s="25" t="n"/>
       <c r="B88" s="25" t="n"/>
       <c r="C88" s="51" t="n"/>
       <c r="D88" s="54" t="n"/>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN N4 (SELECT WI_NAME, ENTRYDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'CancelRevoke') N4 ON N4.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1">
+          <t>LEFT JOIN N3 (SELECT WI_NAME, MIN(ENTRYDATE) AS MIN_APP FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE IN ('CreditApproval','CreditCommittee') GROUP BY WI_NAME) N3 ON N3.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="45" customHeight="1">
       <c r="A89" s="25" t="n"/>
       <c r="B89" s="25" t="n"/>
       <c r="C89" s="51" t="n"/>
       <c r="D89" s="54" t="n"/>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN F.DIMENSION_KEY = A.WORKSTEP_DECISION_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="30" customHeight="1">
+          <t>LEFT JOIN N4 (SELECT WI_NAME, ENTRYDATE FROM STG_FCT_RLOS_WORKSTEP_EVENT WHERE WORKSTEP_CODE = 'CancelRevoke') N4 ON N4.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
       <c r="A90" s="25" t="n"/>
       <c r="B90" s="25" t="n"/>
       <c r="C90" s="51" t="n"/>
       <c r="D90" s="54" t="n"/>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN G.WORKSTEP_CODE = F.WORKSTEP_CODE AND G.DECISION_CODE = F.DECISION_CODE</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1">
+          <t>LEFT JOIN F.DIMENSION_KEY = A.WORKSTEP_DECISION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="25" t="n"/>
       <c r="B91" s="25" t="n"/>
       <c r="C91" s="51" t="n"/>
       <c r="D91" s="54" t="n"/>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN H.STREAM = C.STREAM</t>
+          <t>LEFT JOIN G.WORKSTEP_CODE = F.WORKSTEP_CODE AND G.DECISION_CODE = F.DECISION_CODE</t>
         </is>
       </c>
     </row>
@@ -2737,27 +2753,38 @@
       <c r="D92" s="54" t="n"/>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN J.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="75" customHeight="1">
+          <t>LEFT JOIN H.STREAM = C.STREAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1">
       <c r="A93" s="25" t="n"/>
       <c r="B93" s="25" t="n"/>
       <c r="C93" s="51" t="n"/>
       <c r="D93" s="54" t="n"/>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>LEFT JOIN K ON (K.PRODUCT_LINE = J.PRODUCTLINE_NAME OR (K.PRODUCT_LINE = 'Trường Change Request' AND K.PRODUCT_LINE = A.CHANGE_TYPE)) AND K.DEVIATION_G3 = DEVIATION_G3 (cột cùng bảng) AND K.SECONDARY_PRODUCTLINE = C.IS_SEC_PRODUCT AND K.APP_GRP = C.APP_GRP</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
+          <t>LEFT JOIN J.SUB_PRODUCT_SK = A.SUB_PRODUCT_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="75" customHeight="1">
       <c r="A94" s="25" t="n"/>
       <c r="B94" s="25" t="n"/>
       <c r="C94" s="51" t="n"/>
       <c r="D94" s="54" t="n"/>
       <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN K ON (K.PRODUCT_LINE = J.PRODUCTLINE_NAME OR (K.PRODUCT_LINE = 'Trường Change Request' AND K.PRODUCT_LINE = A.CHANGE_TYPE)) AND K.DEVIATION_G3 = DEVIATION_G3 (cột cùng bảng) AND K.SECONDARY_PRODUCTLINE = C.IS_SEC_PRODUCT AND K.APP_GRP = C.APP_GRP</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="25" t="n"/>
+      <c r="B95" s="25" t="n"/>
+      <c r="C95" s="51" t="n"/>
+      <c r="D95" s="54" t="n"/>
+      <c r="E95" s="8" t="inlineStr">
         <is>
           <t>LEFT JOIN L.WI_NAME = A.WI_NAME</t>
         </is>
